--- a/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_30_4_feb.xlsx
+++ b/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_30_4_feb.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <x:workbookPr codeName="ЭтаКнига"/>
   <x:bookViews>
-    <x:workbookView xWindow="32767" yWindow="32767" windowWidth="23040" windowHeight="8748" firstSheet="0" activeTab="1"/>
+    <x:workbookView xWindow="32760" yWindow="32760" windowWidth="23040" windowHeight="8745" firstSheet="0" activeTab="1"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Основное для всех " sheetId="1" r:id="rId3"/>
@@ -1234,10 +1234,6 @@
 Производственный корпус-Аудитория 25</x:t>
   </x:si>
   <x:si>
-    <x:t>Физическая культура 
-Самсонова Д.А.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Численные методы 
 Литвиненко О.Д. 
 Производственный корпус-Аудитория 27</x:t>
@@ -1660,11 +1656,11 @@
     <x:numFmt numFmtId="7" formatCode="#,##0.00\ &quot;₽&quot;;\-#,##0.00\ &quot;₽&quot;"/>
     <x:numFmt numFmtId="8" formatCode="#,##0.00\ &quot;₽&quot;;[Red]\-#,##0.00\ &quot;₽&quot;"/>
     <x:numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
-    <x:numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <x:numFmt numFmtId="41" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;\ _₽_-;_-@_-"/>
     <x:numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <x:numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <x:numFmt numFmtId="164" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;\ _₽_-;_-@_-"/>
-    <x:numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <x:numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <x:numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <x:numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <x:numFmt numFmtId="166" formatCode="#,##0&quot;р.&quot;;\-#,##0&quot;р.&quot;"/>
     <x:numFmt numFmtId="167" formatCode="#,##0&quot;р.&quot;;[Red]\-#,##0&quot;р.&quot;"/>
     <x:numFmt numFmtId="168" formatCode="#,##0.00&quot;р.&quot;;\-#,##0.00&quot;р.&quot;"/>
@@ -1678,7 +1674,7 @@
     <x:numFmt numFmtId="176" formatCode="&quot;Вкл&quot;;&quot;Вкл&quot;;&quot;Выкл&quot;"/>
     <x:numFmt numFmtId="177" formatCode="[$€-2]\ ###,000_);[Red]\([$€-2]\ ###,000\)"/>
   </x:numFmts>
-  <x:fonts count="47">
+  <x:fonts count="30">
     <x:font>
       <x:sz val="10"/>
       <x:name val="Arial Cyr"/>
@@ -1735,12 +1731,6 @@
     </x:font>
     <x:font>
       <x:sz val="10"/>
-      <x:name val="Arial"/>
-      <x:family val="0"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color indexed="10"/>
       <x:name val="Arial"/>
       <x:family val="0"/>
     </x:font>
@@ -1856,139 +1846,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:sz val="10"/>
+      <x:color indexed="10"/>
+      <x:name val="Arial"/>
+      <x:family val="0"/>
+    </x:font>
+    <x:font>
       <x:b/>
       <x:i/>
       <x:sz val="18"/>
       <x:color rgb="FF0000FF"/>
       <x:name val="Arial"/>
       <x:family val="0"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF006100"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FF7F7F7F"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C0006"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C6500"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color theme="3"/>
-      <x:name val="Cambria"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="3"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="13"/>
-      <x:color theme="3"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="15"/>
-      <x:color theme="3"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F3F"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F76"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
@@ -1998,7 +1867,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2031,25 +1900,25 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.7999799847602844"/>
+        <x:fgColor indexed="27"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.7999799847602844"/>
+        <x:fgColor indexed="47"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.5999900102615356"/>
+        <x:fgColor indexed="44"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.5999900102615356"/>
+        <x:fgColor indexed="29"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -2061,31 +1930,13 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.5999900102615356"/>
+        <x:fgColor indexed="51"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.5999900102615356"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.5999900102615356"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.39998000860214233"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.39998000860214233"/>
+        <x:fgColor indexed="30"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -2097,7 +1948,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.39998000860214233"/>
+        <x:fgColor indexed="49"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -2109,85 +1960,49 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="4"/>
+        <x:fgColor indexed="62"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="5"/>
+        <x:fgColor indexed="10"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="6"/>
+        <x:fgColor indexed="57"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="7"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFCC99"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA5A5A5"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFEB9C"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFC7CE"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFCC"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFC6EFCE"/>
+        <x:fgColor indexed="53"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor indexed="22"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor indexed="55"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor indexed="43"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor indexed="26"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -2202,30 +2017,30 @@
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color indexed="23"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color indexed="23"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color indexed="23"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color indexed="23"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -2239,7 +2054,7 @@
         <x:color indexed="0"/>
       </x:top>
       <x:bottom style="thick">
-        <x:color theme="4"/>
+        <x:color indexed="62"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -2253,7 +2068,7 @@
         <x:color indexed="0"/>
       </x:top>
       <x:bottom style="thick">
-        <x:color theme="4" tint="0.49998000264167786"/>
+        <x:color indexed="22"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -2267,7 +2082,7 @@
         <x:color indexed="0"/>
       </x:top>
       <x:bottom style="medium">
-        <x:color theme="4" tint="0.39998000860214233"/>
+        <x:color indexed="30"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -2278,38 +2093,38 @@
         <x:color indexed="0"/>
       </x:right>
       <x:top style="thin">
-        <x:color theme="4"/>
+        <x:color indexed="62"/>
       </x:top>
       <x:bottom style="double">
-        <x:color theme="4"/>
+        <x:color indexed="62"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="double">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:left>
       <x:right style="double">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:right>
       <x:top style="double">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:top>
       <x:bottom style="double">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFB2B2B2"/>
+        <x:color indexed="22"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FFB2B2B2"/>
+        <x:color indexed="22"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFB2B2B2"/>
+        <x:color indexed="22"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFB2B2B2"/>
+        <x:color indexed="22"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -2323,7 +2138,7 @@
         <x:color indexed="0"/>
       </x:top>
       <x:bottom style="double">
-        <x:color rgb="FFFF8001"/>
+        <x:color indexed="52"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -2402,58 +2217,58 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="43" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="42" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="41" fillId="26" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="13" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="172" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="40" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="39" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="38" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="36" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <x:alignment/>
       <x:protection/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="173" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2472,31 +2287,25 @@
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="12" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="12" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="11" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="32" borderId="11" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="13" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="13" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2508,8 +2317,14 @@
     <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="52">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment/>
     </x:xf>
@@ -2546,59 +2361,59 @@
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" vertical="center"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="center" vertical="center"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="32" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="13" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="13" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
@@ -2636,35 +2451,55 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="12" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="12" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="32" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="13" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="13" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2674,6 +2509,14 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -3128,7 +2971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{62f0d1b3-1804-4f17-a486-b0a0ec3352e7}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{68b9a18f-a004-4640-a881-a0e742bfeded}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr codeName="Лист1">
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -3244,6 +3087,13 @@
       <x:c r="AD2" s="31" t="s"/>
       <x:c r="AE2" s="31" t="s"/>
       <x:c r="AF2" s="31" t="s"/>
+      <x:c r="AG2" s="29" t="s"/>
+      <x:c r="AH2" s="29" t="s"/>
+      <x:c r="AI2" s="29" t="s"/>
+      <x:c r="AJ2" s="29" t="s"/>
+      <x:c r="AK2" s="29" t="s"/>
+      <x:c r="AL2" s="29" t="s"/>
+      <x:c r="AM2" s="29" t="s"/>
       <x:c r="AN2" s="29" t="s"/>
       <x:c r="AO2" s="29" t="s"/>
       <x:c r="AP2" s="29" t="s"/>
@@ -3303,6 +3153,13 @@
       <x:c r="AD3" s="34" t="s"/>
       <x:c r="AE3" s="34" t="s"/>
       <x:c r="AF3" s="34" t="s"/>
+      <x:c r="AG3" s="29" t="s"/>
+      <x:c r="AH3" s="29" t="s"/>
+      <x:c r="AI3" s="29" t="s"/>
+      <x:c r="AJ3" s="29" t="s"/>
+      <x:c r="AK3" s="29" t="s"/>
+      <x:c r="AL3" s="29" t="s"/>
+      <x:c r="AM3" s="29" t="s"/>
       <x:c r="AN3" s="29" t="s"/>
       <x:c r="AO3" s="29" t="s"/>
       <x:c r="AP3" s="29" t="s"/>
@@ -3360,6 +3217,13 @@
       <x:c r="AD4" s="34" t="s"/>
       <x:c r="AE4" s="34" t="s"/>
       <x:c r="AF4" s="34" t="s"/>
+      <x:c r="AG4" s="29" t="s"/>
+      <x:c r="AH4" s="29" t="s"/>
+      <x:c r="AI4" s="29" t="s"/>
+      <x:c r="AJ4" s="29" t="s"/>
+      <x:c r="AK4" s="29" t="s"/>
+      <x:c r="AL4" s="29" t="s"/>
+      <x:c r="AM4" s="29" t="s"/>
       <x:c r="AN4" s="29" t="s"/>
       <x:c r="AO4" s="29" t="s"/>
       <x:c r="AP4" s="29" t="s"/>
@@ -3385,4855 +3249,4855 @@
       <x:c r="BJ4" s="29" t="s"/>
     </x:row>
     <x:row r="5" spans="1:62" s="7" customFormat="1" ht="24.6" customHeight="1">
-      <x:c r="A5" s="12" t="s">
+      <x:c r="A5" s="35" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="12" t="s">
+      <x:c r="B5" s="35" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s">
+      <x:c r="C5" s="36" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D5" s="13" t="s">
+      <x:c r="D5" s="36" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E5" s="13" t="s">
+      <x:c r="E5" s="36" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F5" s="13" t="s">
+      <x:c r="F5" s="36" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G5" s="13" t="s">
+      <x:c r="G5" s="36" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H5" s="13" t="s">
+      <x:c r="H5" s="36" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I5" s="13" t="s">
+      <x:c r="I5" s="36" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J5" s="13" t="s">
+      <x:c r="J5" s="36" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K5" s="13" t="s">
+      <x:c r="K5" s="36" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L5" s="13" t="s">
+      <x:c r="L5" s="36" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M5" s="13" t="s">
+      <x:c r="M5" s="36" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N5" s="13" t="s">
+      <x:c r="N5" s="36" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="O5" s="13" t="s">
+      <x:c r="O5" s="36" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P5" s="13" t="s">
+      <x:c r="P5" s="36" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="Q5" s="13" t="s">
+      <x:c r="Q5" s="36" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="R5" s="13" t="s">
+      <x:c r="R5" s="36" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="S5" s="13" t="s">
+      <x:c r="S5" s="36" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="T5" s="13" t="s">
+      <x:c r="T5" s="36" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="U5" s="13" t="s">
+      <x:c r="U5" s="36" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="V5" s="13" t="s">
+      <x:c r="V5" s="36" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="W5" s="13" t="s">
+      <x:c r="W5" s="36" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="X5" s="13" t="s">
+      <x:c r="X5" s="36" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="Y5" s="13" t="s">
+      <x:c r="Y5" s="36" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="Z5" s="13" t="s">
+      <x:c r="Z5" s="36" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="AA5" s="13" t="s">
+      <x:c r="AA5" s="36" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AB5" s="13" t="s">
+      <x:c r="AB5" s="36" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="AC5" s="13" t="s">
+      <x:c r="AC5" s="36" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="AD5" s="13" t="s">
+      <x:c r="AD5" s="36" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="AE5" s="13" t="s">
+      <x:c r="AE5" s="36" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AF5" s="13" t="s">
+      <x:c r="AF5" s="36" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="AG5" s="13" t="s">
+      <x:c r="AG5" s="36" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="AH5" s="13" t="s">
+      <x:c r="AH5" s="36" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="AI5" s="13" t="s">
+      <x:c r="AI5" s="36" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="AJ5" s="13" t="s">
+      <x:c r="AJ5" s="36" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="AK5" s="13" t="s">
+      <x:c r="AK5" s="36" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="AL5" s="13" t="s">
+      <x:c r="AL5" s="36" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="AM5" s="13" t="s">
+      <x:c r="AM5" s="36" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="AN5" s="13" t="s">
+      <x:c r="AN5" s="36" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="AO5" s="13" t="s">
+      <x:c r="AO5" s="36" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="AP5" s="13" t="s">
+      <x:c r="AP5" s="36" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="AQ5" s="13" t="s">
+      <x:c r="AQ5" s="36" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AR5" s="13" t="s">
+      <x:c r="AR5" s="36" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="AS5" s="13" t="s">
+      <x:c r="AS5" s="36" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="AT5" s="13" t="s">
+      <x:c r="AT5" s="36" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="AU5" s="13" t="s">
+      <x:c r="AU5" s="36" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="AV5" s="13" t="s">
+      <x:c r="AV5" s="36" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="AW5" s="13" t="s">
+      <x:c r="AW5" s="36" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="AX5" s="13" t="s">
+      <x:c r="AX5" s="36" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="AY5" s="13" t="s">
+      <x:c r="AY5" s="36" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="AZ5" s="13" t="s">
+      <x:c r="AZ5" s="36" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="BA5" s="13" t="s">
+      <x:c r="BA5" s="36" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="BB5" s="13" t="s">
+      <x:c r="BB5" s="36" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="BC5" s="13" t="s">
+      <x:c r="BC5" s="36" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="BD5" s="13" t="s">
+      <x:c r="BD5" s="36" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="BE5" s="13" t="s">
+      <x:c r="BE5" s="36" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="BF5" s="13" t="s">
+      <x:c r="BF5" s="36" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="BG5" s="13" t="s">
+      <x:c r="BG5" s="36" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="BH5" s="13" t="s">
+      <x:c r="BH5" s="36" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="BI5" s="13" t="s">
+      <x:c r="BI5" s="36" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="BJ5" s="13" t="s">
+      <x:c r="BJ5" s="36" t="s">
         <x:v>65</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:62" s="7" customFormat="1" ht="79.2" customHeight="1">
-      <x:c r="A6" s="35" t="s">
+    <x:row r="6" spans="1:62" s="7" customFormat="1" ht="76.5" customHeight="1">
+      <x:c r="A6" s="37" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B6" s="36" t="s">
+      <x:c r="B6" s="38" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C6" s="37" t="s">
+      <x:c r="C6" s="50" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D6" s="37" t="s">
+      <x:c r="D6" s="50" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E6" s="38" t="s">
+      <x:c r="E6" s="39" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F6" s="38" t="s">
+      <x:c r="F6" s="39" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G6" s="38" t="s">
+      <x:c r="G6" s="39" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H6" s="38" t="s">
+      <x:c r="H6" s="39" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="I6" s="38" t="s">
+      <x:c r="I6" s="39" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="J6" s="38" t="s">
+      <x:c r="J6" s="39" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="K6" s="38" t="s">
+      <x:c r="K6" s="39" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="L6" s="38" t="s">
+      <x:c r="L6" s="39" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="M6" s="38" t="s">
+      <x:c r="M6" s="39" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N6" s="38" t="s"/>
-      <x:c r="O6" s="38" t="s">
+      <x:c r="N6" s="39" t="s"/>
+      <x:c r="O6" s="39" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="P6" s="38" t="s">
+      <x:c r="P6" s="39" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="Q6" s="38" t="s"/>
-      <x:c r="R6" s="37" t="s">
+      <x:c r="Q6" s="39" t="s"/>
+      <x:c r="R6" s="50" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="S6" s="38" t="s"/>
-      <x:c r="T6" s="38" t="s">
+      <x:c r="S6" s="39" t="s"/>
+      <x:c r="T6" s="39" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="U6" s="39" t="s">
+      <x:c r="U6" s="40" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="V6" s="38" t="s">
+      <x:c r="V6" s="39" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="W6" s="38" t="s">
+      <x:c r="W6" s="39" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="X6" s="38" t="s">
+      <x:c r="X6" s="39" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="Y6" s="38" t="s">
+      <x:c r="Y6" s="39" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="Z6" s="38" t="s">
+      <x:c r="Z6" s="39" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="AA6" s="38" t="s">
+      <x:c r="AA6" s="39" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="AB6" s="38" t="s">
+      <x:c r="AB6" s="39" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AC6" s="38" t="s">
+      <x:c r="AC6" s="39" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="AD6" s="38" t="s">
+      <x:c r="AD6" s="39" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="AE6" s="38" t="s"/>
-      <x:c r="AF6" s="38" t="s">
+      <x:c r="AE6" s="39" t="s"/>
+      <x:c r="AF6" s="39" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="AG6" s="38" t="s"/>
-      <x:c r="AH6" s="38" t="s"/>
-      <x:c r="AI6" s="38" t="s">
+      <x:c r="AG6" s="39" t="s"/>
+      <x:c r="AH6" s="39" t="s"/>
+      <x:c r="AI6" s="39" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="AJ6" s="38" t="s"/>
-      <x:c r="AK6" s="38" t="s"/>
-      <x:c r="AL6" s="38" t="s"/>
-      <x:c r="AM6" s="38" t="s"/>
-      <x:c r="AN6" s="38" t="s"/>
-      <x:c r="AO6" s="38" t="s"/>
-      <x:c r="AP6" s="38" t="s"/>
-      <x:c r="AQ6" s="38" t="s"/>
-      <x:c r="AR6" s="38" t="s"/>
-      <x:c r="AS6" s="38" t="s">
+      <x:c r="AJ6" s="39" t="s"/>
+      <x:c r="AK6" s="39" t="s"/>
+      <x:c r="AL6" s="39" t="s"/>
+      <x:c r="AM6" s="39" t="s"/>
+      <x:c r="AN6" s="39" t="s"/>
+      <x:c r="AO6" s="39" t="s"/>
+      <x:c r="AP6" s="39" t="s"/>
+      <x:c r="AQ6" s="39" t="s"/>
+      <x:c r="AR6" s="39" t="s"/>
+      <x:c r="AS6" s="39" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="AT6" s="38" t="s">
+      <x:c r="AT6" s="39" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="AU6" s="38" t="s">
+      <x:c r="AU6" s="39" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="AV6" s="38" t="s"/>
-      <x:c r="AW6" s="38" t="s"/>
-      <x:c r="AX6" s="38" t="s"/>
-      <x:c r="AY6" s="38" t="s"/>
-      <x:c r="AZ6" s="38" t="s"/>
-      <x:c r="BA6" s="38" t="s">
+      <x:c r="AV6" s="39" t="s"/>
+      <x:c r="AW6" s="39" t="s"/>
+      <x:c r="AX6" s="39" t="s"/>
+      <x:c r="AY6" s="39" t="s"/>
+      <x:c r="AZ6" s="39" t="s"/>
+      <x:c r="BA6" s="39" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="BB6" s="38" t="s"/>
-      <x:c r="BC6" s="38" t="s"/>
-      <x:c r="BD6" s="38" t="s"/>
-      <x:c r="BE6" s="38" t="s"/>
-      <x:c r="BF6" s="38" t="s"/>
-      <x:c r="BG6" s="38" t="s"/>
-      <x:c r="BH6" s="38" t="s"/>
-      <x:c r="BI6" s="38" t="s"/>
-      <x:c r="BJ6" s="38" t="s">
+      <x:c r="BB6" s="39" t="s"/>
+      <x:c r="BC6" s="39" t="s"/>
+      <x:c r="BD6" s="39" t="s"/>
+      <x:c r="BE6" s="39" t="s"/>
+      <x:c r="BF6" s="39" t="s"/>
+      <x:c r="BG6" s="39" t="s"/>
+      <x:c r="BH6" s="39" t="s"/>
+      <x:c r="BI6" s="39" t="s"/>
+      <x:c r="BJ6" s="39" t="s">
         <x:v>98</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:62" s="7" customFormat="1" ht="79.2" customHeight="1">
-      <x:c r="A7" s="40" t="s"/>
-      <x:c r="B7" s="36" t="s">
+    <x:row r="7" spans="1:62" s="7" customFormat="1" ht="63.75" customHeight="1">
+      <x:c r="A7" s="41" t="s"/>
+      <x:c r="B7" s="38" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C7" s="37" t="s">
+      <x:c r="C7" s="50" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D7" s="37" t="s">
+      <x:c r="D7" s="50" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="E7" s="38" t="s">
+      <x:c r="E7" s="39" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="F7" s="38" t="s">
+      <x:c r="F7" s="39" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G7" s="38" t="s">
+      <x:c r="G7" s="39" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H7" s="38" t="s">
+      <x:c r="H7" s="39" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="I7" s="38" t="s">
+      <x:c r="I7" s="39" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="J7" s="38" t="s">
+      <x:c r="J7" s="39" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="K7" s="38" t="s">
+      <x:c r="K7" s="39" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="L7" s="38" t="s">
+      <x:c r="L7" s="39" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="M7" s="38" t="s">
+      <x:c r="M7" s="39" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="N7" s="38" t="s">
+      <x:c r="N7" s="39" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="O7" s="38" t="s">
+      <x:c r="O7" s="39" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="P7" s="38" t="s">
+      <x:c r="P7" s="39" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="Q7" s="39" t="s">
+      <x:c r="Q7" s="40" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="R7" s="37" t="s">
+      <x:c r="R7" s="50" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="S7" s="38" t="s">
+      <x:c r="S7" s="39" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="T7" s="38" t="s">
+      <x:c r="T7" s="39" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="U7" s="38" t="s">
+      <x:c r="U7" s="39" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="V7" s="38" t="s">
+      <x:c r="V7" s="39" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="W7" s="38" t="s">
+      <x:c r="W7" s="39" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="X7" s="38" t="s">
+      <x:c r="X7" s="39" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="Y7" s="38" t="s">
+      <x:c r="Y7" s="39" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="Z7" s="38" t="s">
+      <x:c r="Z7" s="39" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AA7" s="38" t="s">
+      <x:c r="AA7" s="39" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="AB7" s="38" t="s">
+      <x:c r="AB7" s="39" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="AC7" s="38" t="s">
+      <x:c r="AC7" s="39" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="AD7" s="38" t="s">
+      <x:c r="AD7" s="39" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="AE7" s="38" t="s">
+      <x:c r="AE7" s="39" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="AF7" s="38" t="s">
+      <x:c r="AF7" s="39" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="AG7" s="38" t="s">
+      <x:c r="AG7" s="39" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="AH7" s="38" t="s">
+      <x:c r="AH7" s="39" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="AI7" s="38" t="s">
+      <x:c r="AI7" s="39" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="AJ7" s="38" t="s"/>
-      <x:c r="AK7" s="38" t="s">
+      <x:c r="AJ7" s="39" t="s"/>
+      <x:c r="AK7" s="39" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="AL7" s="38" t="s">
+      <x:c r="AL7" s="39" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AM7" s="38" t="s"/>
-      <x:c r="AN7" s="39" t="s">
+      <x:c r="AM7" s="39" t="s"/>
+      <x:c r="AN7" s="40" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="AO7" s="38" t="s"/>
-      <x:c r="AP7" s="38" t="s"/>
-      <x:c r="AQ7" s="38" t="s"/>
-      <x:c r="AR7" s="38" t="s"/>
-      <x:c r="AS7" s="38" t="s">
+      <x:c r="AO7" s="39" t="s"/>
+      <x:c r="AP7" s="39" t="s"/>
+      <x:c r="AQ7" s="39" t="s"/>
+      <x:c r="AR7" s="39" t="s"/>
+      <x:c r="AS7" s="39" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="AT7" s="38" t="s">
+      <x:c r="AT7" s="39" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="AU7" s="38" t="s">
+      <x:c r="AU7" s="39" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="AV7" s="38" t="s"/>
-      <x:c r="AW7" s="38" t="s"/>
-      <x:c r="AX7" s="38" t="s"/>
-      <x:c r="AY7" s="38" t="s">
+      <x:c r="AV7" s="39" t="s"/>
+      <x:c r="AW7" s="39" t="s"/>
+      <x:c r="AX7" s="39" t="s"/>
+      <x:c r="AY7" s="39" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="AZ7" s="38" t="s"/>
-      <x:c r="BA7" s="38" t="s">
+      <x:c r="AZ7" s="39" t="s"/>
+      <x:c r="BA7" s="39" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="BB7" s="38" t="s"/>
-      <x:c r="BC7" s="38" t="s"/>
-      <x:c r="BD7" s="38" t="s"/>
-      <x:c r="BE7" s="38" t="s"/>
-      <x:c r="BF7" s="38" t="s"/>
-      <x:c r="BG7" s="38" t="s">
+      <x:c r="BB7" s="39" t="s"/>
+      <x:c r="BC7" s="39" t="s"/>
+      <x:c r="BD7" s="39" t="s"/>
+      <x:c r="BE7" s="39" t="s"/>
+      <x:c r="BF7" s="39" t="s"/>
+      <x:c r="BG7" s="39" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="BH7" s="38" t="s"/>
-      <x:c r="BI7" s="38" t="s"/>
-      <x:c r="BJ7" s="38" t="s">
+      <x:c r="BH7" s="39" t="s"/>
+      <x:c r="BI7" s="39" t="s"/>
+      <x:c r="BJ7" s="39" t="s">
         <x:v>98</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:62" s="7" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A8" s="40" t="s"/>
-      <x:c r="B8" s="36" t="s">
+    <x:row r="8" spans="1:62" s="7" customFormat="1" ht="63.75" customHeight="1">
+      <x:c r="A8" s="41" t="s"/>
+      <x:c r="B8" s="38" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C8" s="37" t="s">
+      <x:c r="C8" s="50" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D8" s="37" t="s">
+      <x:c r="D8" s="50" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="E8" s="38" t="s">
+      <x:c r="E8" s="39" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F8" s="38" t="s">
+      <x:c r="F8" s="39" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G8" s="38" t="s">
+      <x:c r="G8" s="39" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H8" s="38" t="s">
+      <x:c r="H8" s="39" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="I8" s="38" t="s">
+      <x:c r="I8" s="39" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="J8" s="38" t="s">
+      <x:c r="J8" s="39" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="K8" s="38" t="s">
+      <x:c r="K8" s="39" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="L8" s="38" t="s">
+      <x:c r="L8" s="39" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="M8" s="38" t="s"/>
-      <x:c r="N8" s="38" t="s">
+      <x:c r="M8" s="39" t="s"/>
+      <x:c r="N8" s="39" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="O8" s="38" t="s">
+      <x:c r="O8" s="39" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="P8" s="38" t="s">
+      <x:c r="P8" s="39" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="Q8" s="38" t="s">
+      <x:c r="Q8" s="39" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="R8" s="41" t="s">
+      <x:c r="R8" s="51" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="S8" s="38" t="s">
+      <x:c r="S8" s="39" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="T8" s="39" t="s">
+      <x:c r="T8" s="40" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="U8" s="38" t="s">
+      <x:c r="U8" s="39" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="V8" s="38" t="s">
+      <x:c r="V8" s="39" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="W8" s="38" t="s">
+      <x:c r="W8" s="39" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="X8" s="38" t="s">
+      <x:c r="X8" s="39" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="Y8" s="38" t="s">
+      <x:c r="Y8" s="39" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="Z8" s="38" t="s">
+      <x:c r="Z8" s="39" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="AA8" s="38" t="s">
+      <x:c r="AA8" s="39" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="AB8" s="38" t="s">
+      <x:c r="AB8" s="39" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="AC8" s="38" t="s">
+      <x:c r="AC8" s="39" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="AD8" s="38" t="s">
+      <x:c r="AD8" s="39" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="AE8" s="38" t="s">
+      <x:c r="AE8" s="39" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="AF8" s="38" t="s">
+      <x:c r="AF8" s="39" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="AG8" s="38" t="s">
+      <x:c r="AG8" s="39" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="AH8" s="38" t="s">
+      <x:c r="AH8" s="39" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="AI8" s="38" t="s">
+      <x:c r="AI8" s="39" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="AJ8" s="38" t="s"/>
-      <x:c r="AK8" s="38" t="s">
+      <x:c r="AJ8" s="39" t="s"/>
+      <x:c r="AK8" s="39" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="AL8" s="38" t="s">
+      <x:c r="AL8" s="39" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="AM8" s="38" t="s"/>
-      <x:c r="AN8" s="38" t="s">
+      <x:c r="AM8" s="39" t="s"/>
+      <x:c r="AN8" s="39" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="AO8" s="39" t="s">
+      <x:c r="AO8" s="40" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="AP8" s="38" t="s"/>
-      <x:c r="AQ8" s="39" t="s">
+      <x:c r="AP8" s="39" t="s"/>
+      <x:c r="AQ8" s="40" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="AR8" s="38" t="s">
+      <x:c r="AR8" s="39" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="AS8" s="38" t="s">
+      <x:c r="AS8" s="39" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="AT8" s="38" t="s">
+      <x:c r="AT8" s="39" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="AU8" s="38" t="s">
+      <x:c r="AU8" s="39" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="AV8" s="38" t="s"/>
-      <x:c r="AW8" s="38" t="s"/>
-      <x:c r="AX8" s="38" t="s">
+      <x:c r="AV8" s="39" t="s"/>
+      <x:c r="AW8" s="39" t="s"/>
+      <x:c r="AX8" s="39" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="AY8" s="38" t="s">
+      <x:c r="AY8" s="39" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="AZ8" s="38" t="s"/>
-      <x:c r="BA8" s="38" t="s">
+      <x:c r="AZ8" s="39" t="s"/>
+      <x:c r="BA8" s="39" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="BB8" s="38" t="s">
+      <x:c r="BB8" s="39" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="BC8" s="38" t="s"/>
-      <x:c r="BD8" s="38" t="s"/>
-      <x:c r="BE8" s="38" t="s"/>
-      <x:c r="BF8" s="38" t="s"/>
-      <x:c r="BG8" s="38" t="s">
+      <x:c r="BC8" s="39" t="s"/>
+      <x:c r="BD8" s="39" t="s"/>
+      <x:c r="BE8" s="39" t="s"/>
+      <x:c r="BF8" s="39" t="s"/>
+      <x:c r="BG8" s="39" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="BH8" s="38" t="s"/>
-      <x:c r="BI8" s="38" t="s"/>
-      <x:c r="BJ8" s="38" t="s">
+      <x:c r="BH8" s="39" t="s"/>
+      <x:c r="BI8" s="39" t="s"/>
+      <x:c r="BJ8" s="39" t="s">
         <x:v>153</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A9" s="40" t="s"/>
-      <x:c r="B9" s="36" t="s">
+    <x:row r="9" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A9" s="41" t="s"/>
+      <x:c r="B9" s="38" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C9" s="37" t="s">
+      <x:c r="C9" s="50" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D9" s="38" t="s">
+      <x:c r="D9" s="39" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="E9" s="38" t="s"/>
-      <x:c r="F9" s="38" t="s"/>
-      <x:c r="G9" s="39" t="s">
+      <x:c r="E9" s="39" t="s"/>
+      <x:c r="F9" s="39" t="s"/>
+      <x:c r="G9" s="40" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="H9" s="38" t="s">
+      <x:c r="H9" s="39" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="I9" s="38" t="s"/>
-      <x:c r="J9" s="38" t="s"/>
-      <x:c r="K9" s="38" t="s"/>
-      <x:c r="L9" s="38" t="s"/>
-      <x:c r="M9" s="38" t="s"/>
-      <x:c r="N9" s="38" t="s">
+      <x:c r="I9" s="39" t="s"/>
+      <x:c r="J9" s="39" t="s"/>
+      <x:c r="K9" s="39" t="s"/>
+      <x:c r="L9" s="39" t="s"/>
+      <x:c r="M9" s="39" t="s"/>
+      <x:c r="N9" s="39" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="O9" s="38" t="s"/>
-      <x:c r="P9" s="38" t="s"/>
-      <x:c r="Q9" s="38" t="s">
+      <x:c r="O9" s="39" t="s"/>
+      <x:c r="P9" s="39" t="s"/>
+      <x:c r="Q9" s="39" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="R9" s="37" t="s">
+      <x:c r="R9" s="50" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="S9" s="38" t="s">
+      <x:c r="S9" s="39" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="T9" s="38" t="s">
+      <x:c r="T9" s="39" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="U9" s="38" t="s"/>
-      <x:c r="V9" s="38" t="s"/>
-      <x:c r="W9" s="38" t="s"/>
-      <x:c r="X9" s="39" t="s">
+      <x:c r="U9" s="39" t="s"/>
+      <x:c r="V9" s="39" t="s"/>
+      <x:c r="W9" s="39" t="s"/>
+      <x:c r="X9" s="40" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="Y9" s="38" t="s"/>
-      <x:c r="Z9" s="38" t="s"/>
-      <x:c r="AA9" s="38" t="s"/>
-      <x:c r="AB9" s="38" t="s"/>
-      <x:c r="AC9" s="38" t="s"/>
-      <x:c r="AD9" s="39" t="s"/>
-      <x:c r="AE9" s="38" t="s">
+      <x:c r="Y9" s="39" t="s"/>
+      <x:c r="Z9" s="39" t="s"/>
+      <x:c r="AA9" s="39" t="s"/>
+      <x:c r="AB9" s="39" t="s"/>
+      <x:c r="AC9" s="39" t="s"/>
+      <x:c r="AD9" s="40" t="s"/>
+      <x:c r="AE9" s="39" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AF9" s="39" t="s">
+      <x:c r="AF9" s="40" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="AG9" s="38" t="s">
+      <x:c r="AG9" s="39" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AH9" s="38" t="s">
+      <x:c r="AH9" s="39" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="AI9" s="38" t="s"/>
-      <x:c r="AJ9" s="38" t="s">
+      <x:c r="AI9" s="39" t="s"/>
+      <x:c r="AJ9" s="39" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="AK9" s="38" t="s"/>
-      <x:c r="AL9" s="38" t="s">
+      <x:c r="AK9" s="39" t="s"/>
+      <x:c r="AL9" s="39" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="AM9" s="38" t="s">
+      <x:c r="AM9" s="39" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="AN9" s="38" t="s">
+      <x:c r="AN9" s="39" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="AO9" s="38" t="s">
+      <x:c r="AO9" s="39" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="AP9" s="38" t="s"/>
-      <x:c r="AQ9" s="38" t="s">
+      <x:c r="AP9" s="39" t="s"/>
+      <x:c r="AQ9" s="39" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="AR9" s="38" t="s">
+      <x:c r="AR9" s="39" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="AS9" s="38" t="s"/>
-      <x:c r="AT9" s="38" t="s"/>
-      <x:c r="AU9" s="38" t="s"/>
-      <x:c r="AV9" s="38" t="s">
+      <x:c r="AS9" s="39" t="s"/>
+      <x:c r="AT9" s="39" t="s"/>
+      <x:c r="AU9" s="39" t="s"/>
+      <x:c r="AV9" s="39" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="AW9" s="38" t="s">
+      <x:c r="AW9" s="39" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="AX9" s="38" t="s">
+      <x:c r="AX9" s="39" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="AY9" s="38" t="s">
+      <x:c r="AY9" s="39" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="AZ9" s="38" t="s">
+      <x:c r="AZ9" s="39" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="BA9" s="39" t="s">
+      <x:c r="BA9" s="40" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="BB9" s="38" t="s">
+      <x:c r="BB9" s="39" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="BC9" s="39" t="s">
+      <x:c r="BC9" s="40" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="BD9" s="38" t="s">
+      <x:c r="BD9" s="39" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BE9" s="38" t="s">
+      <x:c r="BE9" s="39" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BF9" s="38" t="s">
+      <x:c r="BF9" s="39" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="BG9" s="38" t="s">
+      <x:c r="BG9" s="39" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="BH9" s="38" t="s">
+      <x:c r="BH9" s="39" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="BI9" s="38" t="s">
+      <x:c r="BI9" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BJ9" s="38" t="s"/>
+      <x:c r="BJ9" s="39" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A10" s="40" t="s"/>
-      <x:c r="B10" s="36" t="s">
+    <x:row r="10" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A10" s="41" t="s"/>
+      <x:c r="B10" s="38" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="C10" s="38" t="s">
+      <x:c r="C10" s="39" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="D10" s="38" t="s">
+      <x:c r="D10" s="39" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="E10" s="38" t="s"/>
-      <x:c r="F10" s="38" t="s"/>
-      <x:c r="G10" s="38" t="s"/>
-      <x:c r="H10" s="38" t="s"/>
-      <x:c r="I10" s="38" t="s"/>
-      <x:c r="J10" s="38" t="s"/>
-      <x:c r="K10" s="38" t="s"/>
-      <x:c r="L10" s="38" t="s"/>
-      <x:c r="M10" s="38" t="s"/>
-      <x:c r="N10" s="38" t="s"/>
-      <x:c r="O10" s="38" t="s"/>
-      <x:c r="P10" s="38" t="s"/>
-      <x:c r="Q10" s="38" t="s"/>
-      <x:c r="R10" s="38" t="s">
+      <x:c r="E10" s="39" t="s"/>
+      <x:c r="F10" s="39" t="s"/>
+      <x:c r="G10" s="39" t="s"/>
+      <x:c r="H10" s="39" t="s"/>
+      <x:c r="I10" s="39" t="s"/>
+      <x:c r="J10" s="39" t="s"/>
+      <x:c r="K10" s="39" t="s"/>
+      <x:c r="L10" s="39" t="s"/>
+      <x:c r="M10" s="39" t="s"/>
+      <x:c r="N10" s="39" t="s"/>
+      <x:c r="O10" s="39" t="s"/>
+      <x:c r="P10" s="39" t="s"/>
+      <x:c r="Q10" s="39" t="s"/>
+      <x:c r="R10" s="39" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="S10" s="38" t="s"/>
-      <x:c r="T10" s="38" t="s"/>
-      <x:c r="U10" s="38" t="s"/>
-      <x:c r="V10" s="38" t="s"/>
-      <x:c r="W10" s="38" t="s"/>
-      <x:c r="X10" s="38" t="s"/>
-      <x:c r="Y10" s="38" t="s"/>
-      <x:c r="Z10" s="38" t="s"/>
-      <x:c r="AA10" s="38" t="s"/>
-      <x:c r="AB10" s="38" t="s"/>
-      <x:c r="AC10" s="38" t="s"/>
-      <x:c r="AD10" s="38" t="s"/>
-      <x:c r="AE10" s="38" t="s"/>
-      <x:c r="AF10" s="38" t="s"/>
-      <x:c r="AG10" s="39" t="s">
+      <x:c r="S10" s="39" t="s"/>
+      <x:c r="T10" s="39" t="s"/>
+      <x:c r="U10" s="39" t="s"/>
+      <x:c r="V10" s="39" t="s"/>
+      <x:c r="W10" s="39" t="s"/>
+      <x:c r="X10" s="39" t="s"/>
+      <x:c r="Y10" s="39" t="s"/>
+      <x:c r="Z10" s="39" t="s"/>
+      <x:c r="AA10" s="39" t="s"/>
+      <x:c r="AB10" s="39" t="s"/>
+      <x:c r="AC10" s="39" t="s"/>
+      <x:c r="AD10" s="39" t="s"/>
+      <x:c r="AE10" s="39" t="s"/>
+      <x:c r="AF10" s="39" t="s"/>
+      <x:c r="AG10" s="40" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="AH10" s="38" t="s"/>
-      <x:c r="AI10" s="38" t="s"/>
-      <x:c r="AJ10" s="38" t="s">
+      <x:c r="AH10" s="39" t="s"/>
+      <x:c r="AI10" s="39" t="s"/>
+      <x:c r="AJ10" s="39" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="AK10" s="38" t="s"/>
-      <x:c r="AL10" s="38" t="s">
+      <x:c r="AK10" s="39" t="s"/>
+      <x:c r="AL10" s="39" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="AM10" s="38" t="s">
+      <x:c r="AM10" s="39" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="AN10" s="38" t="s">
+      <x:c r="AN10" s="39" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="AO10" s="38" t="s">
+      <x:c r="AO10" s="39" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="AP10" s="38" t="s"/>
-      <x:c r="AQ10" s="38" t="s">
+      <x:c r="AP10" s="39" t="s"/>
+      <x:c r="AQ10" s="39" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="AR10" s="38" t="s">
+      <x:c r="AR10" s="39" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="AS10" s="38" t="s"/>
-      <x:c r="AT10" s="38" t="s"/>
-      <x:c r="AU10" s="38" t="s"/>
-      <x:c r="AV10" s="38" t="s">
+      <x:c r="AS10" s="39" t="s"/>
+      <x:c r="AT10" s="39" t="s"/>
+      <x:c r="AU10" s="39" t="s"/>
+      <x:c r="AV10" s="39" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="AW10" s="38" t="s">
+      <x:c r="AW10" s="39" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="AX10" s="38" t="s">
+      <x:c r="AX10" s="39" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="AY10" s="38" t="s"/>
-      <x:c r="AZ10" s="38" t="s">
+      <x:c r="AY10" s="39" t="s"/>
+      <x:c r="AZ10" s="39" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="BA10" s="38" t="s"/>
-      <x:c r="BB10" s="38" t="s">
+      <x:c r="BA10" s="39" t="s"/>
+      <x:c r="BB10" s="39" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="BC10" s="38" t="s">
+      <x:c r="BC10" s="39" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="BD10" s="38" t="s">
+      <x:c r="BD10" s="39" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="BE10" s="38" t="s">
+      <x:c r="BE10" s="39" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="BF10" s="38" t="s">
+      <x:c r="BF10" s="39" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="BG10" s="38" t="s"/>
-      <x:c r="BH10" s="38" t="s">
+      <x:c r="BG10" s="39" t="s"/>
+      <x:c r="BH10" s="39" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="BI10" s="38" t="s">
+      <x:c r="BI10" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BJ10" s="38" t="s"/>
+      <x:c r="BJ10" s="39" t="s"/>
     </x:row>
-    <x:row r="11" spans="1:62" ht="53.4" customHeight="1">
+    <x:row r="11" spans="1:62" ht="53.45" customHeight="1">
       <x:c r="A11" s="42" t="s"/>
-      <x:c r="B11" s="36" t="s">
+      <x:c r="B11" s="38" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="C11" s="38" t="s">
+      <x:c r="C11" s="39" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="D11" s="38" t="s">
+      <x:c r="D11" s="39" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="E11" s="38" t="s"/>
-      <x:c r="F11" s="38" t="s"/>
-      <x:c r="G11" s="38" t="s"/>
-      <x:c r="H11" s="38" t="s"/>
-      <x:c r="I11" s="38" t="s"/>
-      <x:c r="J11" s="38" t="s"/>
-      <x:c r="K11" s="38" t="s"/>
-      <x:c r="L11" s="38" t="s"/>
-      <x:c r="M11" s="38" t="s"/>
-      <x:c r="N11" s="38" t="s"/>
-      <x:c r="O11" s="38" t="s"/>
-      <x:c r="P11" s="38" t="s"/>
-      <x:c r="Q11" s="38" t="s"/>
-      <x:c r="R11" s="38" t="s">
+      <x:c r="E11" s="39" t="s"/>
+      <x:c r="F11" s="39" t="s"/>
+      <x:c r="G11" s="39" t="s"/>
+      <x:c r="H11" s="39" t="s"/>
+      <x:c r="I11" s="39" t="s"/>
+      <x:c r="J11" s="39" t="s"/>
+      <x:c r="K11" s="39" t="s"/>
+      <x:c r="L11" s="39" t="s"/>
+      <x:c r="M11" s="39" t="s"/>
+      <x:c r="N11" s="39" t="s"/>
+      <x:c r="O11" s="39" t="s"/>
+      <x:c r="P11" s="39" t="s"/>
+      <x:c r="Q11" s="39" t="s"/>
+      <x:c r="R11" s="39" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="S11" s="38" t="s"/>
-      <x:c r="T11" s="38" t="s"/>
-      <x:c r="U11" s="38" t="s"/>
-      <x:c r="V11" s="38" t="s"/>
-      <x:c r="W11" s="38" t="s"/>
-      <x:c r="X11" s="38" t="s"/>
-      <x:c r="Y11" s="38" t="s"/>
-      <x:c r="Z11" s="38" t="s"/>
-      <x:c r="AA11" s="38" t="s"/>
-      <x:c r="AB11" s="38" t="s"/>
-      <x:c r="AC11" s="38" t="s"/>
-      <x:c r="AD11" s="38" t="s"/>
-      <x:c r="AE11" s="38" t="s"/>
-      <x:c r="AF11" s="38" t="s"/>
-      <x:c r="AG11" s="38" t="s"/>
-      <x:c r="AH11" s="38" t="s"/>
-      <x:c r="AI11" s="38" t="s"/>
-      <x:c r="AJ11" s="38" t="s">
+      <x:c r="S11" s="39" t="s"/>
+      <x:c r="T11" s="39" t="s"/>
+      <x:c r="U11" s="39" t="s"/>
+      <x:c r="V11" s="39" t="s"/>
+      <x:c r="W11" s="39" t="s"/>
+      <x:c r="X11" s="39" t="s"/>
+      <x:c r="Y11" s="39" t="s"/>
+      <x:c r="Z11" s="39" t="s"/>
+      <x:c r="AA11" s="39" t="s"/>
+      <x:c r="AB11" s="39" t="s"/>
+      <x:c r="AC11" s="39" t="s"/>
+      <x:c r="AD11" s="39" t="s"/>
+      <x:c r="AE11" s="39" t="s"/>
+      <x:c r="AF11" s="39" t="s"/>
+      <x:c r="AG11" s="39" t="s"/>
+      <x:c r="AH11" s="39" t="s"/>
+      <x:c r="AI11" s="39" t="s"/>
+      <x:c r="AJ11" s="39" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="AK11" s="38" t="s"/>
-      <x:c r="AL11" s="38" t="s"/>
-      <x:c r="AM11" s="38" t="s">
+      <x:c r="AK11" s="39" t="s"/>
+      <x:c r="AL11" s="39" t="s"/>
+      <x:c r="AM11" s="39" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="AN11" s="38" t="s"/>
-      <x:c r="AO11" s="38" t="s">
+      <x:c r="AN11" s="39" t="s"/>
+      <x:c r="AO11" s="39" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="AP11" s="38" t="s"/>
-      <x:c r="AQ11" s="38" t="s">
+      <x:c r="AP11" s="39" t="s"/>
+      <x:c r="AQ11" s="39" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="AR11" s="38" t="s"/>
-      <x:c r="AS11" s="38" t="s"/>
-      <x:c r="AT11" s="38" t="s"/>
-      <x:c r="AU11" s="38" t="s"/>
-      <x:c r="AV11" s="38" t="s">
+      <x:c r="AR11" s="39" t="s"/>
+      <x:c r="AS11" s="39" t="s"/>
+      <x:c r="AT11" s="39" t="s"/>
+      <x:c r="AU11" s="39" t="s"/>
+      <x:c r="AV11" s="39" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="AW11" s="38" t="s">
+      <x:c r="AW11" s="39" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="AX11" s="38" t="s"/>
-      <x:c r="AY11" s="38" t="s"/>
-      <x:c r="AZ11" s="38" t="s">
+      <x:c r="AX11" s="39" t="s"/>
+      <x:c r="AY11" s="39" t="s"/>
+      <x:c r="AZ11" s="39" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="BA11" s="38" t="s"/>
-      <x:c r="BB11" s="38" t="s"/>
-      <x:c r="BC11" s="38" t="s">
+      <x:c r="BA11" s="39" t="s"/>
+      <x:c r="BB11" s="39" t="s"/>
+      <x:c r="BC11" s="39" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="BD11" s="38" t="s">
+      <x:c r="BD11" s="39" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="BE11" s="38" t="s">
+      <x:c r="BE11" s="39" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="BF11" s="38" t="s"/>
-      <x:c r="BG11" s="38" t="s"/>
-      <x:c r="BH11" s="38" t="s">
+      <x:c r="BF11" s="39" t="s"/>
+      <x:c r="BG11" s="39" t="s"/>
+      <x:c r="BH11" s="39" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="BI11" s="38" t="s">
+      <x:c r="BI11" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BJ11" s="38" t="s"/>
+      <x:c r="BJ11" s="39" t="s"/>
     </x:row>
-    <x:row r="12" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A12" s="23" t="s">
+    <x:row r="12" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A12" s="43" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="B12" s="13" t="s">
+      <x:c r="B12" s="36" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="C12" s="44" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D12" s="14" t="s">
+      <x:c r="D12" s="44" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="E12" s="44" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="F12" s="44" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="G12" s="44" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H12" s="14" t="s">
+      <x:c r="H12" s="44" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="I12" s="14" t="s">
+      <x:c r="I12" s="44" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="J12" s="14" t="s">
+      <x:c r="J12" s="44" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="s">
+      <x:c r="K12" s="44" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="L12" s="14" t="s"/>
-      <x:c r="M12" s="14" t="s">
+      <x:c r="L12" s="44" t="s"/>
+      <x:c r="M12" s="44" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="N12" s="14" t="s"/>
-      <x:c r="O12" s="14" t="s"/>
-      <x:c r="P12" s="14" t="s">
+      <x:c r="N12" s="44" t="s"/>
+      <x:c r="O12" s="44" t="s"/>
+      <x:c r="P12" s="44" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="Q12" s="14" t="s">
+      <x:c r="Q12" s="44" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="R12" s="14" t="s"/>
-      <x:c r="S12" s="14" t="s">
+      <x:c r="R12" s="44" t="s"/>
+      <x:c r="S12" s="44" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="T12" s="14" t="s">
+      <x:c r="T12" s="44" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="U12" s="14" t="s">
+      <x:c r="U12" s="44" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="V12" s="18" t="s">
+      <x:c r="V12" s="45" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="W12" s="14" t="s"/>
-      <x:c r="X12" s="14" t="s"/>
-      <x:c r="Y12" s="14" t="s">
+      <x:c r="W12" s="44" t="s"/>
+      <x:c r="X12" s="44" t="s"/>
+      <x:c r="Y12" s="44" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="Z12" s="14" t="s">
+      <x:c r="Z12" s="44" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="AA12" s="14" t="s">
+      <x:c r="AA12" s="44" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="AB12" s="14" t="s">
+      <x:c r="AB12" s="44" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="AC12" s="14" t="s">
+      <x:c r="AC12" s="44" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="AD12" s="14" t="s"/>
-      <x:c r="AE12" s="14" t="s">
+      <x:c r="AD12" s="44" t="s"/>
+      <x:c r="AE12" s="44" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="AF12" s="14" t="s">
+      <x:c r="AF12" s="44" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="AG12" s="14" t="s">
+      <x:c r="AG12" s="44" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="AH12" s="14" t="s">
+      <x:c r="AH12" s="44" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="AI12" s="14" t="s"/>
-      <x:c r="AJ12" s="14" t="s"/>
-      <x:c r="AK12" s="14" t="s">
+      <x:c r="AI12" s="44" t="s"/>
+      <x:c r="AJ12" s="44" t="s"/>
+      <x:c r="AK12" s="44" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="AL12" s="14" t="s">
+      <x:c r="AL12" s="44" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AM12" s="14" t="s"/>
-      <x:c r="AN12" s="14" t="s"/>
-      <x:c r="AO12" s="14" t="s">
+      <x:c r="AM12" s="44" t="s"/>
+      <x:c r="AN12" s="44" t="s"/>
+      <x:c r="AO12" s="44" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="AP12" s="14" t="s"/>
-      <x:c r="AQ12" s="14" t="s"/>
-      <x:c r="AR12" s="14" t="s">
+      <x:c r="AP12" s="44" t="s"/>
+      <x:c r="AQ12" s="44" t="s"/>
+      <x:c r="AR12" s="44" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="AS12" s="14" t="s"/>
-      <x:c r="AT12" s="14" t="s"/>
-      <x:c r="AU12" s="14" t="s">
+      <x:c r="AS12" s="44" t="s"/>
+      <x:c r="AT12" s="44" t="s"/>
+      <x:c r="AU12" s="44" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="AV12" s="14" t="s"/>
-      <x:c r="AW12" s="14" t="s"/>
-      <x:c r="AX12" s="14" t="s"/>
-      <x:c r="AY12" s="14" t="s"/>
-      <x:c r="AZ12" s="14" t="s"/>
-      <x:c r="BA12" s="14" t="s"/>
-      <x:c r="BB12" s="14" t="s"/>
-      <x:c r="BC12" s="14" t="s"/>
-      <x:c r="BD12" s="14" t="s"/>
-      <x:c r="BE12" s="14" t="s">
+      <x:c r="AV12" s="44" t="s"/>
+      <x:c r="AW12" s="44" t="s"/>
+      <x:c r="AX12" s="44" t="s"/>
+      <x:c r="AY12" s="44" t="s"/>
+      <x:c r="AZ12" s="44" t="s"/>
+      <x:c r="BA12" s="44" t="s"/>
+      <x:c r="BB12" s="44" t="s"/>
+      <x:c r="BC12" s="44" t="s"/>
+      <x:c r="BD12" s="44" t="s"/>
+      <x:c r="BE12" s="44" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="BF12" s="14" t="s"/>
-      <x:c r="BG12" s="14" t="s"/>
-      <x:c r="BH12" s="14" t="s"/>
-      <x:c r="BI12" s="14" t="s"/>
-      <x:c r="BJ12" s="14" t="s"/>
+      <x:c r="BF12" s="44" t="s"/>
+      <x:c r="BG12" s="44" t="s"/>
+      <x:c r="BH12" s="44" t="s"/>
+      <x:c r="BI12" s="44" t="s"/>
+      <x:c r="BJ12" s="44" t="s"/>
     </x:row>
-    <x:row r="13" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A13" s="24" t="s"/>
-      <x:c r="B13" s="13" t="s">
+    <x:row r="13" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A13" s="46" t="s"/>
+      <x:c r="B13" s="36" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="C13" s="44" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="s">
+      <x:c r="D13" s="44" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="E13" s="44" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="F13" s="44" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="G13" s="44" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="H13" s="14" t="s">
+      <x:c r="H13" s="44" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="I13" s="14" t="s">
+      <x:c r="I13" s="44" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="J13" s="14" t="s">
+      <x:c r="J13" s="44" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="s">
+      <x:c r="K13" s="44" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="L13" s="14" t="s"/>
-      <x:c r="M13" s="14" t="s">
+      <x:c r="L13" s="44" t="s"/>
+      <x:c r="M13" s="44" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="N13" s="14" t="s">
+      <x:c r="N13" s="44" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="O13" s="14" t="s">
+      <x:c r="O13" s="44" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="P13" s="14" t="s">
+      <x:c r="P13" s="44" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="Q13" s="14" t="s">
+      <x:c r="Q13" s="44" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="R13" s="14" t="s">
+      <x:c r="R13" s="44" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="S13" s="14" t="s">
+      <x:c r="S13" s="44" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="T13" s="14" t="s">
+      <x:c r="T13" s="44" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="U13" s="14" t="s">
+      <x:c r="U13" s="44" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="V13" s="14" t="s">
+      <x:c r="V13" s="44" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="W13" s="14" t="s">
+      <x:c r="W13" s="44" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="X13" s="14" t="s">
+      <x:c r="X13" s="44" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="Y13" s="14" t="s">
+      <x:c r="Y13" s="44" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="Z13" s="14" t="s">
+      <x:c r="Z13" s="44" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="AA13" s="14" t="s">
+      <x:c r="AA13" s="44" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="AB13" s="14" t="s">
+      <x:c r="AB13" s="44" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="AC13" s="14" t="s">
+      <x:c r="AC13" s="44" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AD13" s="14" t="s">
+      <x:c r="AD13" s="44" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="AE13" s="14" t="s">
+      <x:c r="AE13" s="44" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="AF13" s="14" t="s">
+      <x:c r="AF13" s="44" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="AG13" s="14" t="s">
+      <x:c r="AG13" s="44" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="AH13" s="14" t="s">
+      <x:c r="AH13" s="44" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AI13" s="14" t="s"/>
-      <x:c r="AJ13" s="18" t="s"/>
-      <x:c r="AK13" s="14" t="s">
+      <x:c r="AI13" s="44" t="s"/>
+      <x:c r="AJ13" s="45" t="s"/>
+      <x:c r="AK13" s="44" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="AL13" s="14" t="s">
+      <x:c r="AL13" s="44" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="AM13" s="14" t="s"/>
-      <x:c r="AN13" s="14" t="s"/>
-      <x:c r="AO13" s="14" t="s">
+      <x:c r="AM13" s="44" t="s"/>
+      <x:c r="AN13" s="44" t="s"/>
+      <x:c r="AO13" s="44" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="AP13" s="14" t="s"/>
-      <x:c r="AQ13" s="14" t="s"/>
-      <x:c r="AR13" s="14" t="s">
+      <x:c r="AP13" s="44" t="s"/>
+      <x:c r="AQ13" s="44" t="s"/>
+      <x:c r="AR13" s="44" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="AS13" s="14" t="s"/>
-      <x:c r="AT13" s="14" t="s"/>
-      <x:c r="AU13" s="14" t="s">
+      <x:c r="AS13" s="44" t="s"/>
+      <x:c r="AT13" s="44" t="s"/>
+      <x:c r="AU13" s="44" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="AV13" s="14" t="s"/>
-      <x:c r="AW13" s="14" t="s"/>
-      <x:c r="AX13" s="14" t="s">
+      <x:c r="AV13" s="44" t="s"/>
+      <x:c r="AW13" s="44" t="s"/>
+      <x:c r="AX13" s="44" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="AY13" s="14" t="s">
+      <x:c r="AY13" s="44" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="AZ13" s="14" t="s"/>
-      <x:c r="BA13" s="14" t="s"/>
-      <x:c r="BB13" s="14" t="s"/>
-      <x:c r="BC13" s="14" t="s"/>
-      <x:c r="BD13" s="14" t="s"/>
-      <x:c r="BE13" s="14" t="s">
+      <x:c r="AZ13" s="44" t="s"/>
+      <x:c r="BA13" s="44" t="s"/>
+      <x:c r="BB13" s="44" t="s"/>
+      <x:c r="BC13" s="44" t="s"/>
+      <x:c r="BD13" s="44" t="s"/>
+      <x:c r="BE13" s="44" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="BF13" s="14" t="s">
+      <x:c r="BF13" s="44" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="BG13" s="14" t="s"/>
-      <x:c r="BH13" s="14" t="s"/>
-      <x:c r="BI13" s="14" t="s"/>
-      <x:c r="BJ13" s="14" t="s"/>
+      <x:c r="BG13" s="44" t="s"/>
+      <x:c r="BH13" s="44" t="s"/>
+      <x:c r="BI13" s="44" t="s"/>
+      <x:c r="BJ13" s="44" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A14" s="24" t="s"/>
-      <x:c r="B14" s="13" t="s">
+    <x:row r="14" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A14" s="46" t="s"/>
+      <x:c r="B14" s="36" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="C14" s="44" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="s">
+      <x:c r="D14" s="44" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="E14" s="44" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="F14" s="44" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="G14" s="44" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="H14" s="14" t="s">
+      <x:c r="H14" s="44" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="I14" s="14" t="s">
+      <x:c r="I14" s="44" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="J14" s="14" t="s">
+      <x:c r="J14" s="44" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="s">
+      <x:c r="K14" s="44" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="L14" s="14" t="s">
+      <x:c r="L14" s="44" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
+      <x:c r="M14" s="44" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="N14" s="14" t="s">
+      <x:c r="N14" s="44" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="O14" s="14" t="s">
+      <x:c r="O14" s="44" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="P14" s="14" t="s">
+      <x:c r="P14" s="44" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="Q14" s="14" t="s">
+      <x:c r="Q14" s="44" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="R14" s="14" t="s">
+      <x:c r="R14" s="44" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="S14" s="14" t="s">
+      <x:c r="S14" s="44" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="T14" s="14" t="s">
+      <x:c r="T14" s="44" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="U14" s="14" t="s">
+      <x:c r="U14" s="44" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="V14" s="14" t="s">
+      <x:c r="V14" s="44" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="W14" s="14" t="s">
+      <x:c r="W14" s="44" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="X14" s="14" t="s">
+      <x:c r="X14" s="44" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="Y14" s="14" t="s">
+      <x:c r="Y14" s="44" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="Z14" s="14" t="s">
+      <x:c r="Z14" s="44" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="AA14" s="14" t="s">
+      <x:c r="AA14" s="44" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AB14" s="14" t="s">
+      <x:c r="AB14" s="44" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="AC14" s="14" t="s">
+      <x:c r="AC14" s="44" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="AD14" s="14" t="s">
+      <x:c r="AD14" s="44" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="AE14" s="14" t="s">
+      <x:c r="AE14" s="44" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AF14" s="14" t="s">
+      <x:c r="AF14" s="44" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="AG14" s="14" t="s">
+      <x:c r="AG14" s="44" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="AH14" s="14" t="s">
+      <x:c r="AH14" s="44" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="AI14" s="14" t="s">
+      <x:c r="AI14" s="44" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="AJ14" s="14" t="s">
+      <x:c r="AJ14" s="44" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="AK14" s="14" t="s">
+      <x:c r="AK14" s="44" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="AL14" s="18" t="s">
+      <x:c r="AL14" s="45" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="AM14" s="14" t="s"/>
-      <x:c r="AN14" s="14" t="s"/>
-      <x:c r="AO14" s="14" t="s">
+      <x:c r="AM14" s="44" t="s"/>
+      <x:c r="AN14" s="44" t="s"/>
+      <x:c r="AO14" s="44" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="AP14" s="14" t="s"/>
-      <x:c r="AQ14" s="14" t="s">
+      <x:c r="AP14" s="44" t="s"/>
+      <x:c r="AQ14" s="44" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="AR14" s="14" t="s">
+      <x:c r="AR14" s="44" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="AS14" s="14" t="s"/>
-      <x:c r="AT14" s="14" t="s"/>
-      <x:c r="AU14" s="14" t="s">
+      <x:c r="AS14" s="44" t="s"/>
+      <x:c r="AT14" s="44" t="s"/>
+      <x:c r="AU14" s="44" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="AV14" s="14" t="s"/>
-      <x:c r="AW14" s="14" t="s"/>
-      <x:c r="AX14" s="14" t="s">
+      <x:c r="AV14" s="44" t="s"/>
+      <x:c r="AW14" s="44" t="s"/>
+      <x:c r="AX14" s="44" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="AY14" s="14" t="s">
+      <x:c r="AY14" s="44" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="AZ14" s="14" t="s"/>
-      <x:c r="BA14" s="14" t="s"/>
-      <x:c r="BB14" s="14" t="s">
+      <x:c r="AZ14" s="44" t="s"/>
+      <x:c r="BA14" s="44" t="s"/>
+      <x:c r="BB14" s="44" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BC14" s="14" t="s"/>
-      <x:c r="BD14" s="14" t="s"/>
-      <x:c r="BE14" s="14" t="s">
+      <x:c r="BC14" s="44" t="s"/>
+      <x:c r="BD14" s="44" t="s"/>
+      <x:c r="BE14" s="44" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="BF14" s="14" t="s">
+      <x:c r="BF14" s="44" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="BG14" s="14" t="s"/>
-      <x:c r="BH14" s="14" t="s"/>
-      <x:c r="BI14" s="14" t="s"/>
-      <x:c r="BJ14" s="14" t="s"/>
+      <x:c r="BG14" s="44" t="s"/>
+      <x:c r="BH14" s="44" t="s"/>
+      <x:c r="BI14" s="44" t="s"/>
+      <x:c r="BJ14" s="44" t="s"/>
     </x:row>
-    <x:row r="15" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A15" s="24" t="s"/>
-      <x:c r="B15" s="13" t="s">
+    <x:row r="15" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A15" s="46" t="s"/>
+      <x:c r="B15" s="36" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s"/>
-      <x:c r="D15" s="14" t="s"/>
-      <x:c r="E15" s="18" t="s">
+      <x:c r="C15" s="44" t="s"/>
+      <x:c r="D15" s="44" t="s"/>
+      <x:c r="E15" s="45" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s"/>
-      <x:c r="G15" s="14" t="s"/>
-      <x:c r="H15" s="14" t="s"/>
-      <x:c r="I15" s="14" t="s"/>
-      <x:c r="J15" s="14" t="s"/>
-      <x:c r="K15" s="14" t="s"/>
-      <x:c r="L15" s="14" t="s">
+      <x:c r="F15" s="44" t="s"/>
+      <x:c r="G15" s="44" t="s"/>
+      <x:c r="H15" s="44" t="s"/>
+      <x:c r="I15" s="44" t="s"/>
+      <x:c r="J15" s="44" t="s"/>
+      <x:c r="K15" s="44" t="s"/>
+      <x:c r="L15" s="44" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s"/>
-      <x:c r="N15" s="14" t="s">
+      <x:c r="M15" s="44" t="s"/>
+      <x:c r="N15" s="44" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="O15" s="14" t="s">
+      <x:c r="O15" s="44" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="P15" s="14" t="s"/>
-      <x:c r="Q15" s="14" t="s">
+      <x:c r="P15" s="44" t="s"/>
+      <x:c r="Q15" s="44" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="R15" s="14" t="s"/>
-      <x:c r="S15" s="14" t="s"/>
-      <x:c r="T15" s="14" t="s"/>
-      <x:c r="U15" s="14" t="s"/>
-      <x:c r="V15" s="14" t="s">
+      <x:c r="R15" s="44" t="s"/>
+      <x:c r="S15" s="44" t="s"/>
+      <x:c r="T15" s="44" t="s"/>
+      <x:c r="U15" s="44" t="s"/>
+      <x:c r="V15" s="44" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="W15" s="14" t="s">
+      <x:c r="W15" s="44" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="X15" s="14" t="s">
+      <x:c r="X15" s="44" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="Y15" s="14" t="s"/>
-      <x:c r="Z15" s="14" t="s"/>
-      <x:c r="AA15" s="14" t="s">
+      <x:c r="Y15" s="44" t="s"/>
+      <x:c r="Z15" s="44" t="s"/>
+      <x:c r="AA15" s="44" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="AB15" s="14" t="s"/>
-      <x:c r="AC15" s="14" t="s"/>
-      <x:c r="AD15" s="14" t="s">
+      <x:c r="AB15" s="44" t="s"/>
+      <x:c r="AC15" s="44" t="s"/>
+      <x:c r="AD15" s="44" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="AE15" s="14" t="s"/>
-      <x:c r="AF15" s="14" t="s">
+      <x:c r="AE15" s="44" t="s"/>
+      <x:c r="AF15" s="44" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AG15" s="14" t="s">
+      <x:c r="AG15" s="44" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="AH15" s="14" t="s"/>
-      <x:c r="AI15" s="14" t="s">
+      <x:c r="AH15" s="44" t="s"/>
+      <x:c r="AI15" s="44" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="AJ15" s="14" t="s">
+      <x:c r="AJ15" s="44" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="AK15" s="14" t="s"/>
-      <x:c r="AL15" s="14" t="s"/>
-      <x:c r="AM15" s="14" t="s">
+      <x:c r="AK15" s="44" t="s"/>
+      <x:c r="AL15" s="44" t="s"/>
+      <x:c r="AM15" s="44" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="AN15" s="14" t="s">
+      <x:c r="AN15" s="44" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="AO15" s="14" t="s"/>
-      <x:c r="AP15" s="14" t="s"/>
-      <x:c r="AQ15" s="14" t="s">
+      <x:c r="AO15" s="44" t="s"/>
+      <x:c r="AP15" s="44" t="s"/>
+      <x:c r="AQ15" s="44" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="AR15" s="14" t="s"/>
-      <x:c r="AS15" s="14" t="s">
+      <x:c r="AR15" s="44" t="s"/>
+      <x:c r="AS15" s="44" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="AT15" s="14" t="s">
+      <x:c r="AT15" s="44" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="AU15" s="14" t="s"/>
-      <x:c r="AV15" s="14" t="s">
+      <x:c r="AU15" s="44" t="s"/>
+      <x:c r="AV15" s="44" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="AW15" s="14" t="s">
+      <x:c r="AW15" s="44" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="AX15" s="14" t="s">
+      <x:c r="AX15" s="44" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="AY15" s="14" t="s">
+      <x:c r="AY15" s="44" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="AZ15" s="18" t="s">
+      <x:c r="AZ15" s="45" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="BA15" s="14" t="s">
+      <x:c r="BA15" s="44" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="BB15" s="14" t="s">
+      <x:c r="BB15" s="44" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BC15" s="14" t="s">
+      <x:c r="BC15" s="44" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="BD15" s="14" t="s">
+      <x:c r="BD15" s="44" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="BE15" s="14" t="s"/>
-      <x:c r="BF15" s="14" t="s">
+      <x:c r="BE15" s="44" t="s"/>
+      <x:c r="BF15" s="44" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="BG15" s="14" t="s">
+      <x:c r="BG15" s="44" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="BH15" s="14" t="s">
+      <x:c r="BH15" s="44" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BI15" s="14" t="s">
+      <x:c r="BI15" s="44" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="BJ15" s="14" t="s">
+      <x:c r="BJ15" s="44" t="s">
         <x:v>214</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A16" s="24" t="s"/>
-      <x:c r="B16" s="13" t="s">
+    <x:row r="16" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A16" s="46" t="s"/>
+      <x:c r="B16" s="36" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="s"/>
-      <x:c r="D16" s="14" t="s"/>
-      <x:c r="E16" s="14" t="s"/>
-      <x:c r="F16" s="14" t="s"/>
-      <x:c r="G16" s="14" t="s"/>
-      <x:c r="H16" s="14" t="s"/>
-      <x:c r="I16" s="14" t="s"/>
-      <x:c r="J16" s="14" t="s"/>
-      <x:c r="K16" s="14" t="s"/>
-      <x:c r="L16" s="14" t="s">
+      <x:c r="C16" s="44" t="s"/>
+      <x:c r="D16" s="44" t="s"/>
+      <x:c r="E16" s="44" t="s"/>
+      <x:c r="F16" s="44" t="s"/>
+      <x:c r="G16" s="44" t="s"/>
+      <x:c r="H16" s="44" t="s"/>
+      <x:c r="I16" s="44" t="s"/>
+      <x:c r="J16" s="44" t="s"/>
+      <x:c r="K16" s="44" t="s"/>
+      <x:c r="L16" s="44" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s"/>
-      <x:c r="N16" s="14" t="s"/>
-      <x:c r="O16" s="14" t="s"/>
-      <x:c r="P16" s="14" t="s"/>
-      <x:c r="Q16" s="14" t="s"/>
-      <x:c r="R16" s="14" t="s"/>
-      <x:c r="S16" s="14" t="s"/>
-      <x:c r="T16" s="14" t="s"/>
-      <x:c r="U16" s="14" t="s"/>
-      <x:c r="V16" s="14" t="s"/>
-      <x:c r="W16" s="14" t="s"/>
-      <x:c r="X16" s="14" t="s"/>
-      <x:c r="Y16" s="14" t="s"/>
-      <x:c r="Z16" s="14" t="s"/>
-      <x:c r="AA16" s="14" t="s"/>
-      <x:c r="AB16" s="14" t="s"/>
-      <x:c r="AC16" s="14" t="s"/>
-      <x:c r="AD16" s="18" t="s">
+      <x:c r="M16" s="44" t="s"/>
+      <x:c r="N16" s="44" t="s"/>
+      <x:c r="O16" s="44" t="s"/>
+      <x:c r="P16" s="44" t="s"/>
+      <x:c r="Q16" s="44" t="s"/>
+      <x:c r="R16" s="44" t="s"/>
+      <x:c r="S16" s="44" t="s"/>
+      <x:c r="T16" s="44" t="s"/>
+      <x:c r="U16" s="44" t="s"/>
+      <x:c r="V16" s="44" t="s"/>
+      <x:c r="W16" s="44" t="s"/>
+      <x:c r="X16" s="44" t="s"/>
+      <x:c r="Y16" s="44" t="s"/>
+      <x:c r="Z16" s="44" t="s"/>
+      <x:c r="AA16" s="44" t="s"/>
+      <x:c r="AB16" s="44" t="s"/>
+      <x:c r="AC16" s="44" t="s"/>
+      <x:c r="AD16" s="45" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="AE16" s="14" t="s"/>
-      <x:c r="AF16" s="14" t="s"/>
-      <x:c r="AG16" s="14" t="s"/>
-      <x:c r="AH16" s="14" t="s"/>
-      <x:c r="AI16" s="14" t="s">
+      <x:c r="AE16" s="44" t="s"/>
+      <x:c r="AF16" s="44" t="s"/>
+      <x:c r="AG16" s="44" t="s"/>
+      <x:c r="AH16" s="44" t="s"/>
+      <x:c r="AI16" s="44" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AJ16" s="14" t="s">
+      <x:c r="AJ16" s="44" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="AK16" s="14" t="s"/>
-      <x:c r="AL16" s="14" t="s"/>
-      <x:c r="AM16" s="14" t="s">
+      <x:c r="AK16" s="44" t="s"/>
+      <x:c r="AL16" s="44" t="s"/>
+      <x:c r="AM16" s="44" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="AN16" s="14" t="s">
+      <x:c r="AN16" s="44" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="AO16" s="14" t="s"/>
-      <x:c r="AP16" s="14" t="s"/>
-      <x:c r="AQ16" s="14" t="s">
+      <x:c r="AO16" s="44" t="s"/>
+      <x:c r="AP16" s="44" t="s"/>
+      <x:c r="AQ16" s="44" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="AR16" s="14" t="s"/>
-      <x:c r="AS16" s="14" t="s">
+      <x:c r="AR16" s="44" t="s"/>
+      <x:c r="AS16" s="44" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="AT16" s="14" t="s">
+      <x:c r="AT16" s="44" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="AU16" s="14" t="s"/>
-      <x:c r="AV16" s="14" t="s">
+      <x:c r="AU16" s="44" t="s"/>
+      <x:c r="AV16" s="44" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="AW16" s="14" t="s">
+      <x:c r="AW16" s="44" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="AX16" s="14" t="s"/>
-      <x:c r="AY16" s="14" t="s"/>
-      <x:c r="AZ16" s="14" t="s">
+      <x:c r="AX16" s="44" t="s"/>
+      <x:c r="AY16" s="44" t="s"/>
+      <x:c r="AZ16" s="44" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="BA16" s="14" t="s">
+      <x:c r="BA16" s="44" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="BB16" s="14" t="s">
+      <x:c r="BB16" s="44" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="BC16" s="14" t="s">
+      <x:c r="BC16" s="44" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="BD16" s="14" t="s">
+      <x:c r="BD16" s="44" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="BE16" s="14" t="s"/>
-      <x:c r="BF16" s="14" t="s"/>
-      <x:c r="BG16" s="14" t="s">
+      <x:c r="BE16" s="44" t="s"/>
+      <x:c r="BF16" s="44" t="s"/>
+      <x:c r="BG16" s="44" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="BH16" s="14" t="s">
+      <x:c r="BH16" s="44" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BI16" s="14" t="s">
+      <x:c r="BI16" s="44" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="BJ16" s="14" t="s">
+      <x:c r="BJ16" s="44" t="s">
         <x:v>153</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A17" s="25" t="s"/>
-      <x:c r="B17" s="13" t="s">
+    <x:row r="17" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A17" s="47" t="s"/>
+      <x:c r="B17" s="36" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="C17" s="14" t="s"/>
-      <x:c r="D17" s="14" t="s"/>
-      <x:c r="E17" s="14" t="s"/>
-      <x:c r="F17" s="14" t="s"/>
-      <x:c r="G17" s="14" t="s"/>
-      <x:c r="H17" s="14" t="s"/>
-      <x:c r="I17" s="14" t="s"/>
-      <x:c r="J17" s="14" t="s"/>
-      <x:c r="K17" s="14" t="s"/>
-      <x:c r="L17" s="14" t="s"/>
-      <x:c r="M17" s="14" t="s"/>
-      <x:c r="N17" s="14" t="s"/>
-      <x:c r="O17" s="14" t="s"/>
-      <x:c r="P17" s="14" t="s"/>
-      <x:c r="Q17" s="14" t="s"/>
-      <x:c r="R17" s="14" t="s"/>
-      <x:c r="S17" s="14" t="s"/>
-      <x:c r="T17" s="14" t="s"/>
-      <x:c r="U17" s="14" t="s"/>
-      <x:c r="V17" s="14" t="s"/>
-      <x:c r="W17" s="14" t="s"/>
-      <x:c r="X17" s="14" t="s"/>
-      <x:c r="Y17" s="14" t="s"/>
-      <x:c r="Z17" s="14" t="s"/>
-      <x:c r="AA17" s="14" t="s"/>
-      <x:c r="AB17" s="14" t="s"/>
-      <x:c r="AC17" s="14" t="s"/>
-      <x:c r="AD17" s="14" t="s"/>
-      <x:c r="AE17" s="14" t="s"/>
-      <x:c r="AF17" s="14" t="s"/>
-      <x:c r="AG17" s="14" t="s"/>
-      <x:c r="AH17" s="14" t="s"/>
-      <x:c r="AI17" s="14" t="s"/>
-      <x:c r="AJ17" s="14" t="s"/>
-      <x:c r="AK17" s="14" t="s"/>
-      <x:c r="AL17" s="14" t="s"/>
-      <x:c r="AM17" s="14" t="s">
+      <x:c r="C17" s="44" t="s"/>
+      <x:c r="D17" s="44" t="s"/>
+      <x:c r="E17" s="44" t="s"/>
+      <x:c r="F17" s="44" t="s"/>
+      <x:c r="G17" s="44" t="s"/>
+      <x:c r="H17" s="44" t="s"/>
+      <x:c r="I17" s="44" t="s"/>
+      <x:c r="J17" s="44" t="s"/>
+      <x:c r="K17" s="44" t="s"/>
+      <x:c r="L17" s="44" t="s"/>
+      <x:c r="M17" s="44" t="s"/>
+      <x:c r="N17" s="44" t="s"/>
+      <x:c r="O17" s="44" t="s"/>
+      <x:c r="P17" s="44" t="s"/>
+      <x:c r="Q17" s="44" t="s"/>
+      <x:c r="R17" s="44" t="s"/>
+      <x:c r="S17" s="44" t="s"/>
+      <x:c r="T17" s="44" t="s"/>
+      <x:c r="U17" s="44" t="s"/>
+      <x:c r="V17" s="44" t="s"/>
+      <x:c r="W17" s="44" t="s"/>
+      <x:c r="X17" s="44" t="s"/>
+      <x:c r="Y17" s="44" t="s"/>
+      <x:c r="Z17" s="44" t="s"/>
+      <x:c r="AA17" s="44" t="s"/>
+      <x:c r="AB17" s="44" t="s"/>
+      <x:c r="AC17" s="44" t="s"/>
+      <x:c r="AD17" s="44" t="s"/>
+      <x:c r="AE17" s="44" t="s"/>
+      <x:c r="AF17" s="44" t="s"/>
+      <x:c r="AG17" s="44" t="s"/>
+      <x:c r="AH17" s="44" t="s"/>
+      <x:c r="AI17" s="44" t="s"/>
+      <x:c r="AJ17" s="44" t="s"/>
+      <x:c r="AK17" s="44" t="s"/>
+      <x:c r="AL17" s="44" t="s"/>
+      <x:c r="AM17" s="44" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="AN17" s="14" t="s">
+      <x:c r="AN17" s="44" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="AO17" s="14" t="s"/>
-      <x:c r="AP17" s="14" t="s"/>
-      <x:c r="AQ17" s="14" t="s"/>
-      <x:c r="AR17" s="14" t="s"/>
-      <x:c r="AS17" s="14" t="s">
+      <x:c r="AO17" s="44" t="s"/>
+      <x:c r="AP17" s="44" t="s"/>
+      <x:c r="AQ17" s="44" t="s"/>
+      <x:c r="AR17" s="44" t="s"/>
+      <x:c r="AS17" s="44" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="AT17" s="14" t="s">
+      <x:c r="AT17" s="44" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="AU17" s="14" t="s"/>
-      <x:c r="AV17" s="14" t="s">
+      <x:c r="AU17" s="44" t="s"/>
+      <x:c r="AV17" s="44" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="AW17" s="14" t="s">
+      <x:c r="AW17" s="44" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="AX17" s="14" t="s"/>
-      <x:c r="AY17" s="14" t="s"/>
-      <x:c r="AZ17" s="14" t="s">
+      <x:c r="AX17" s="44" t="s"/>
+      <x:c r="AY17" s="44" t="s"/>
+      <x:c r="AZ17" s="44" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="BA17" s="14" t="s">
+      <x:c r="BA17" s="44" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="BB17" s="14" t="s"/>
-      <x:c r="BC17" s="14" t="s">
+      <x:c r="BB17" s="44" t="s"/>
+      <x:c r="BC17" s="44" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BD17" s="14" t="s">
+      <x:c r="BD17" s="44" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="BE17" s="14" t="s"/>
-      <x:c r="BF17" s="14" t="s"/>
-      <x:c r="BG17" s="14" t="s">
+      <x:c r="BE17" s="44" t="s"/>
+      <x:c r="BF17" s="44" t="s"/>
+      <x:c r="BG17" s="44" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="BH17" s="14" t="s">
+      <x:c r="BH17" s="44" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BI17" s="14" t="s">
+      <x:c r="BI17" s="44" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="BJ17" s="14" t="s">
+      <x:c r="BJ17" s="44" t="s">
         <x:v>87</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:62" ht="79.2" customHeight="1">
-      <x:c r="A18" s="35" t="s">
+    <x:row r="18" spans="1:62" ht="63.75" customHeight="1">
+      <x:c r="A18" s="37" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="B18" s="36" t="s">
+      <x:c r="B18" s="38" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C18" s="38" t="s">
+      <x:c r="C18" s="39" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="D18" s="38" t="s">
+      <x:c r="D18" s="39" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="E18" s="38" t="s"/>
-      <x:c r="F18" s="38" t="s">
+      <x:c r="E18" s="39" t="s"/>
+      <x:c r="F18" s="39" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G18" s="38" t="s">
+      <x:c r="G18" s="39" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H18" s="38" t="s">
+      <x:c r="H18" s="39" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="I18" s="38" t="s">
+      <x:c r="I18" s="39" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="J18" s="38" t="s">
+      <x:c r="J18" s="39" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="K18" s="38" t="s">
+      <x:c r="K18" s="39" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="L18" s="38" t="s">
+      <x:c r="L18" s="39" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="M18" s="38" t="s">
+      <x:c r="M18" s="39" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="N18" s="38" t="s">
+      <x:c r="N18" s="39" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="O18" s="38" t="s">
+      <x:c r="O18" s="39" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="P18" s="38" t="s">
+      <x:c r="P18" s="39" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="Q18" s="38" t="s"/>
-      <x:c r="R18" s="39" t="s">
+      <x:c r="Q18" s="39" t="s"/>
+      <x:c r="R18" s="40" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="S18" s="38" t="s">
+      <x:c r="S18" s="39" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="T18" s="38" t="s">
+      <x:c r="T18" s="39" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="U18" s="38" t="s"/>
-      <x:c r="V18" s="38" t="s">
+      <x:c r="U18" s="39" t="s"/>
+      <x:c r="V18" s="39" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="W18" s="38" t="s"/>
-      <x:c r="X18" s="38" t="s">
+      <x:c r="W18" s="39" t="s"/>
+      <x:c r="X18" s="39" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="Y18" s="38" t="s">
+      <x:c r="Y18" s="39" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="Z18" s="38" t="s">
+      <x:c r="Z18" s="39" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="AA18" s="39" t="s">
+      <x:c r="AA18" s="40" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="AB18" s="38" t="s">
+      <x:c r="AB18" s="39" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="AC18" s="38" t="s"/>
-      <x:c r="AD18" s="38" t="s"/>
-      <x:c r="AE18" s="38" t="s"/>
-      <x:c r="AF18" s="38" t="s"/>
-      <x:c r="AG18" s="38" t="s"/>
-      <x:c r="AH18" s="39" t="s">
+      <x:c r="AC18" s="39" t="s"/>
+      <x:c r="AD18" s="39" t="s"/>
+      <x:c r="AE18" s="39" t="s"/>
+      <x:c r="AF18" s="39" t="s"/>
+      <x:c r="AG18" s="39" t="s"/>
+      <x:c r="AH18" s="40" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="AI18" s="38" t="s">
+      <x:c r="AI18" s="39" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="AJ18" s="38" t="s"/>
-      <x:c r="AK18" s="38" t="s"/>
-      <x:c r="AL18" s="38" t="s"/>
-      <x:c r="AM18" s="38" t="s"/>
-      <x:c r="AN18" s="38" t="s"/>
-      <x:c r="AO18" s="38" t="s"/>
-      <x:c r="AP18" s="38" t="s"/>
-      <x:c r="AQ18" s="38" t="s">
+      <x:c r="AJ18" s="39" t="s"/>
+      <x:c r="AK18" s="39" t="s"/>
+      <x:c r="AL18" s="39" t="s"/>
+      <x:c r="AM18" s="39" t="s"/>
+      <x:c r="AN18" s="39" t="s"/>
+      <x:c r="AO18" s="39" t="s"/>
+      <x:c r="AP18" s="39" t="s"/>
+      <x:c r="AQ18" s="39" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="AR18" s="38" t="s"/>
-      <x:c r="AS18" s="38" t="s"/>
-      <x:c r="AT18" s="38" t="s"/>
-      <x:c r="AU18" s="38" t="s"/>
-      <x:c r="AV18" s="38" t="s"/>
-      <x:c r="AW18" s="38" t="s"/>
-      <x:c r="AX18" s="38" t="s"/>
-      <x:c r="AY18" s="38" t="s"/>
-      <x:c r="AZ18" s="38" t="s"/>
-      <x:c r="BA18" s="38" t="s"/>
-      <x:c r="BB18" s="38" t="s"/>
-      <x:c r="BC18" s="38" t="s"/>
-      <x:c r="BD18" s="38" t="s">
+      <x:c r="AR18" s="39" t="s"/>
+      <x:c r="AS18" s="39" t="s"/>
+      <x:c r="AT18" s="39" t="s"/>
+      <x:c r="AU18" s="39" t="s"/>
+      <x:c r="AV18" s="39" t="s"/>
+      <x:c r="AW18" s="39" t="s"/>
+      <x:c r="AX18" s="39" t="s"/>
+      <x:c r="AY18" s="39" t="s"/>
+      <x:c r="AZ18" s="39" t="s"/>
+      <x:c r="BA18" s="39" t="s"/>
+      <x:c r="BB18" s="39" t="s"/>
+      <x:c r="BC18" s="39" t="s"/>
+      <x:c r="BD18" s="39" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="BE18" s="38" t="s">
+      <x:c r="BE18" s="39" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BF18" s="38" t="s"/>
-      <x:c r="BG18" s="38" t="s">
+      <x:c r="BF18" s="39" t="s"/>
+      <x:c r="BG18" s="39" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="BH18" s="38" t="s">
+      <x:c r="BH18" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BI18" s="38" t="s">
+      <x:c r="BI18" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BJ18" s="38" t="s"/>
+      <x:c r="BJ18" s="39" t="s"/>
     </x:row>
-    <x:row r="19" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A19" s="40" t="s"/>
-      <x:c r="B19" s="36" t="s">
+    <x:row r="19" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A19" s="41" t="s"/>
+      <x:c r="B19" s="38" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C19" s="38" t="s">
+      <x:c r="C19" s="39" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D19" s="38" t="s">
+      <x:c r="D19" s="39" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E19" s="38" t="s"/>
-      <x:c r="F19" s="38" t="s">
+      <x:c r="E19" s="39" t="s"/>
+      <x:c r="F19" s="39" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="G19" s="38" t="s">
+      <x:c r="G19" s="39" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H19" s="38" t="s">
+      <x:c r="H19" s="39" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="I19" s="38" t="s">
+      <x:c r="I19" s="39" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="J19" s="38" t="s">
+      <x:c r="J19" s="39" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="K19" s="38" t="s">
+      <x:c r="K19" s="39" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="L19" s="38" t="s">
+      <x:c r="L19" s="39" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="M19" s="38" t="s">
+      <x:c r="M19" s="39" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="N19" s="38" t="s">
+      <x:c r="N19" s="39" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="O19" s="38" t="s">
+      <x:c r="O19" s="39" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="P19" s="38" t="s">
+      <x:c r="P19" s="39" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="Q19" s="38" t="s">
+      <x:c r="Q19" s="39" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="R19" s="38" t="s">
+      <x:c r="R19" s="39" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="S19" s="38" t="s">
+      <x:c r="S19" s="39" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="T19" s="38" t="s">
+      <x:c r="T19" s="39" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="U19" s="38" t="s">
+      <x:c r="U19" s="39" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="V19" s="38" t="s">
+      <x:c r="V19" s="39" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="W19" s="38" t="s">
+      <x:c r="W19" s="39" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="X19" s="38" t="s">
+      <x:c r="X19" s="39" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="Y19" s="38" t="s">
+      <x:c r="Y19" s="39" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="Z19" s="38" t="s">
+      <x:c r="Z19" s="39" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="AA19" s="38" t="s">
+      <x:c r="AA19" s="39" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="AB19" s="38" t="s">
+      <x:c r="AB19" s="39" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="AC19" s="38" t="s">
+      <x:c r="AC19" s="39" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="AD19" s="38" t="s">
+      <x:c r="AD19" s="39" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AE19" s="38" t="s">
+      <x:c r="AE19" s="39" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="AF19" s="38" t="s">
+      <x:c r="AF19" s="39" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="AG19" s="38" t="s">
+      <x:c r="AG19" s="39" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="AH19" s="38" t="s">
+      <x:c r="AH19" s="39" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="AI19" s="38" t="s">
+      <x:c r="AI19" s="39" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="AJ19" s="39" t="s">
+      <x:c r="AJ19" s="40" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="AK19" s="38" t="s"/>
-      <x:c r="AL19" s="38" t="s"/>
-      <x:c r="AM19" s="38" t="s">
+      <x:c r="AK19" s="39" t="s"/>
+      <x:c r="AL19" s="39" t="s"/>
+      <x:c r="AM19" s="39" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="AN19" s="38" t="s">
+      <x:c r="AN19" s="39" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="AO19" s="38" t="s"/>
-      <x:c r="AP19" s="38" t="s"/>
-      <x:c r="AQ19" s="38" t="s">
+      <x:c r="AO19" s="39" t="s"/>
+      <x:c r="AP19" s="39" t="s"/>
+      <x:c r="AQ19" s="39" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="AR19" s="38" t="s"/>
-      <x:c r="AS19" s="38" t="s"/>
-      <x:c r="AT19" s="38" t="s"/>
-      <x:c r="AU19" s="38" t="s"/>
-      <x:c r="AV19" s="38" t="s"/>
-      <x:c r="AW19" s="38" t="s"/>
-      <x:c r="AX19" s="38" t="s"/>
-      <x:c r="AY19" s="38" t="s"/>
-      <x:c r="AZ19" s="38" t="s"/>
-      <x:c r="BA19" s="38" t="s"/>
-      <x:c r="BB19" s="38" t="s"/>
-      <x:c r="BC19" s="38" t="s"/>
-      <x:c r="BD19" s="38" t="s">
+      <x:c r="AR19" s="39" t="s"/>
+      <x:c r="AS19" s="39" t="s"/>
+      <x:c r="AT19" s="39" t="s"/>
+      <x:c r="AU19" s="39" t="s"/>
+      <x:c r="AV19" s="39" t="s"/>
+      <x:c r="AW19" s="39" t="s"/>
+      <x:c r="AX19" s="39" t="s"/>
+      <x:c r="AY19" s="39" t="s"/>
+      <x:c r="AZ19" s="39" t="s"/>
+      <x:c r="BA19" s="39" t="s"/>
+      <x:c r="BB19" s="39" t="s"/>
+      <x:c r="BC19" s="39" t="s"/>
+      <x:c r="BD19" s="39" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BE19" s="38" t="s">
+      <x:c r="BE19" s="39" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BF19" s="38" t="s">
+      <x:c r="BF19" s="39" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="BG19" s="38" t="s">
+      <x:c r="BG19" s="39" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="BH19" s="38" t="s">
+      <x:c r="BH19" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BI19" s="38" t="s">
+      <x:c r="BI19" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BJ19" s="38" t="s"/>
+      <x:c r="BJ19" s="39" t="s"/>
     </x:row>
-    <x:row r="20" spans="1:62" ht="66" customHeight="1">
-      <x:c r="A20" s="40" t="s"/>
-      <x:c r="B20" s="36" t="s">
+    <x:row r="20" spans="1:62" ht="63.75" customHeight="1">
+      <x:c r="A20" s="41" t="s"/>
+      <x:c r="B20" s="38" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C20" s="38" t="s">
+      <x:c r="C20" s="39" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D20" s="38" t="s">
+      <x:c r="D20" s="39" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="E20" s="38" t="s">
+      <x:c r="E20" s="39" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="F20" s="38" t="s">
+      <x:c r="F20" s="39" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G20" s="38" t="s">
+      <x:c r="G20" s="39" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="H20" s="38" t="s">
+      <x:c r="H20" s="39" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="I20" s="38" t="s">
+      <x:c r="I20" s="39" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="J20" s="38" t="s">
+      <x:c r="J20" s="39" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="K20" s="38" t="s">
+      <x:c r="K20" s="39" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="L20" s="38" t="s">
+      <x:c r="L20" s="39" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="M20" s="38" t="s">
+      <x:c r="M20" s="39" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="N20" s="38" t="s">
+      <x:c r="N20" s="39" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="O20" s="38" t="s">
+      <x:c r="O20" s="39" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="P20" s="38" t="s">
+      <x:c r="P20" s="39" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="Q20" s="38" t="s">
+      <x:c r="Q20" s="39" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="R20" s="38" t="s">
+      <x:c r="R20" s="39" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="S20" s="38" t="s">
+      <x:c r="S20" s="39" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="T20" s="38" t="s">
+      <x:c r="T20" s="39" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="U20" s="38" t="s">
+      <x:c r="U20" s="39" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="V20" s="38" t="s">
+      <x:c r="V20" s="39" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="W20" s="38" t="s">
+      <x:c r="W20" s="39" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="X20" s="38" t="s">
+      <x:c r="X20" s="39" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="Y20" s="38" t="s">
+      <x:c r="Y20" s="39" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="Z20" s="38" t="s">
+      <x:c r="Z20" s="39" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="AA20" s="38" t="s">
+      <x:c r="AA20" s="39" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="AB20" s="38" t="s">
+      <x:c r="AB20" s="39" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="AC20" s="38" t="s">
+      <x:c r="AC20" s="39" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="AD20" s="38" t="s">
+      <x:c r="AD20" s="39" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="AE20" s="38" t="s">
+      <x:c r="AE20" s="39" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="AF20" s="38" t="s">
+      <x:c r="AF20" s="39" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="AG20" s="38" t="s">
+      <x:c r="AG20" s="39" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="AH20" s="38" t="s">
+      <x:c r="AH20" s="39" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="AI20" s="38" t="s">
+      <x:c r="AI20" s="39" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="AJ20" s="38" t="s">
+      <x:c r="AJ20" s="39" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AK20" s="38" t="s">
+      <x:c r="AK20" s="39" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="AL20" s="38" t="s"/>
-      <x:c r="AM20" s="38" t="s">
+      <x:c r="AL20" s="39" t="s"/>
+      <x:c r="AM20" s="39" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="AN20" s="38" t="s">
+      <x:c r="AN20" s="39" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="AO20" s="38" t="s">
+      <x:c r="AO20" s="39" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="AP20" s="38" t="s"/>
-      <x:c r="AQ20" s="38" t="s">
+      <x:c r="AP20" s="39" t="s"/>
+      <x:c r="AQ20" s="39" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="AR20" s="38" t="s"/>
-      <x:c r="AS20" s="38" t="s"/>
-      <x:c r="AT20" s="39" t="s">
+      <x:c r="AR20" s="39" t="s"/>
+      <x:c r="AS20" s="39" t="s"/>
+      <x:c r="AT20" s="40" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="AU20" s="38" t="s"/>
-      <x:c r="AV20" s="38" t="s"/>
-      <x:c r="AW20" s="38" t="s"/>
-      <x:c r="AX20" s="38" t="s">
+      <x:c r="AU20" s="39" t="s"/>
+      <x:c r="AV20" s="39" t="s"/>
+      <x:c r="AW20" s="39" t="s"/>
+      <x:c r="AX20" s="39" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="AY20" s="38" t="s">
+      <x:c r="AY20" s="39" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="AZ20" s="38" t="s"/>
-      <x:c r="BA20" s="39" t="s">
+      <x:c r="AZ20" s="39" t="s"/>
+      <x:c r="BA20" s="40" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="BB20" s="38" t="s"/>
-      <x:c r="BC20" s="38" t="s"/>
-      <x:c r="BD20" s="38" t="s">
+      <x:c r="BB20" s="39" t="s"/>
+      <x:c r="BC20" s="39" t="s"/>
+      <x:c r="BD20" s="39" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="BE20" s="38" t="s">
+      <x:c r="BE20" s="39" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="BF20" s="38" t="s">
+      <x:c r="BF20" s="39" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="BG20" s="38" t="s">
+      <x:c r="BG20" s="39" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="BH20" s="38" t="s">
+      <x:c r="BH20" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BI20" s="38" t="s">
+      <x:c r="BI20" s="39" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="BJ20" s="38" t="s"/>
+      <x:c r="BJ20" s="39" t="s"/>
     </x:row>
-    <x:row r="21" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A21" s="40" t="s"/>
-      <x:c r="B21" s="36" t="s">
+    <x:row r="21" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A21" s="41" t="s"/>
+      <x:c r="B21" s="38" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C21" s="39" t="s">
+      <x:c r="C21" s="40" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D21" s="38" t="s"/>
-      <x:c r="E21" s="38" t="s">
+      <x:c r="D21" s="39" t="s"/>
+      <x:c r="E21" s="39" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="F21" s="38" t="s"/>
-      <x:c r="G21" s="38" t="s"/>
-      <x:c r="H21" s="38" t="s"/>
-      <x:c r="I21" s="38" t="s">
+      <x:c r="F21" s="39" t="s"/>
+      <x:c r="G21" s="39" t="s"/>
+      <x:c r="H21" s="39" t="s"/>
+      <x:c r="I21" s="39" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="J21" s="38" t="s"/>
-      <x:c r="K21" s="38" t="s"/>
-      <x:c r="L21" s="38" t="s"/>
-      <x:c r="M21" s="38" t="s">
+      <x:c r="J21" s="39" t="s"/>
+      <x:c r="K21" s="39" t="s"/>
+      <x:c r="L21" s="39" t="s"/>
+      <x:c r="M21" s="39" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="N21" s="38" t="s"/>
-      <x:c r="O21" s="38" t="s"/>
-      <x:c r="P21" s="38" t="s"/>
-      <x:c r="Q21" s="38" t="s">
+      <x:c r="N21" s="39" t="s"/>
+      <x:c r="O21" s="39" t="s"/>
+      <x:c r="P21" s="39" t="s"/>
+      <x:c r="Q21" s="39" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="R21" s="38" t="s">
+      <x:c r="R21" s="39" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="S21" s="38" t="s"/>
-      <x:c r="T21" s="38" t="s"/>
-      <x:c r="U21" s="38" t="s">
+      <x:c r="S21" s="39" t="s"/>
+      <x:c r="T21" s="39" t="s"/>
+      <x:c r="U21" s="39" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="V21" s="38" t="s"/>
-      <x:c r="W21" s="38" t="s">
+      <x:c r="V21" s="39" t="s"/>
+      <x:c r="W21" s="39" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="X21" s="38" t="s"/>
-      <x:c r="Y21" s="39" t="s">
+      <x:c r="X21" s="39" t="s"/>
+      <x:c r="Y21" s="40" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="Z21" s="38" t="s"/>
-      <x:c r="AA21" s="38" t="s"/>
-      <x:c r="AB21" s="38" t="s">
+      <x:c r="Z21" s="39" t="s"/>
+      <x:c r="AA21" s="39" t="s"/>
+      <x:c r="AB21" s="39" t="s"/>
+      <x:c r="AC21" s="39" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="AD21" s="39" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="AC21" s="38" t="s">
+      <x:c r="AE21" s="39" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="AF21" s="39" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="AG21" s="39" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="AH21" s="39" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="AI21" s="39" t="s"/>
+      <x:c r="AJ21" s="39" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="AK21" s="39" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="AL21" s="39" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="AM21" s="39" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AN21" s="39" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="AO21" s="39" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AP21" s="39" t="s"/>
+      <x:c r="AQ21" s="39" t="s"/>
+      <x:c r="AR21" s="39" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="AS21" s="39" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="AT21" s="39" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="AU21" s="39" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="AV21" s="39" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="AW21" s="39" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="AX21" s="39" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="AY21" s="39" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AZ21" s="39" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA21" s="39" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="BB21" s="39" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="BC21" s="39" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="BD21" s="39" t="s"/>
+      <x:c r="BE21" s="39" t="s"/>
+      <x:c r="BF21" s="39" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="BG21" s="40" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="BH21" s="39" t="s"/>
+      <x:c r="BI21" s="39" t="s"/>
+      <x:c r="BJ21" s="39" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A22" s="41" t="s"/>
+      <x:c r="B22" s="38" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C22" s="39" t="s"/>
+      <x:c r="D22" s="39" t="s"/>
+      <x:c r="E22" s="39" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F22" s="39" t="s"/>
+      <x:c r="G22" s="39" t="s"/>
+      <x:c r="H22" s="39" t="s"/>
+      <x:c r="I22" s="39" t="s"/>
+      <x:c r="J22" s="39" t="s"/>
+      <x:c r="K22" s="39" t="s"/>
+      <x:c r="L22" s="39" t="s"/>
+      <x:c r="M22" s="39" t="s"/>
+      <x:c r="N22" s="39" t="s"/>
+      <x:c r="O22" s="39" t="s"/>
+      <x:c r="P22" s="39" t="s"/>
+      <x:c r="Q22" s="39" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="R22" s="39" t="s"/>
+      <x:c r="S22" s="39" t="s"/>
+      <x:c r="T22" s="39" t="s"/>
+      <x:c r="U22" s="39" t="s"/>
+      <x:c r="V22" s="39" t="s"/>
+      <x:c r="W22" s="39" t="s"/>
+      <x:c r="X22" s="39" t="s"/>
+      <x:c r="Y22" s="39" t="s"/>
+      <x:c r="Z22" s="39" t="s"/>
+      <x:c r="AA22" s="39" t="s"/>
+      <x:c r="AB22" s="39" t="s"/>
+      <x:c r="AC22" s="39" t="s"/>
+      <x:c r="AD22" s="39" t="s"/>
+      <x:c r="AE22" s="39" t="s"/>
+      <x:c r="AF22" s="39" t="s"/>
+      <x:c r="AG22" s="39" t="s"/>
+      <x:c r="AH22" s="39" t="s"/>
+      <x:c r="AI22" s="39" t="s"/>
+      <x:c r="AJ22" s="39" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AK22" s="39" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="AL22" s="39" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="AM22" s="39" t="s"/>
+      <x:c r="AN22" s="39" t="s"/>
+      <x:c r="AO22" s="39" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="AP22" s="39" t="s"/>
+      <x:c r="AQ22" s="39" t="s"/>
+      <x:c r="AR22" s="39" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="AS22" s="39" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="AT22" s="39" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="AU22" s="39" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="AV22" s="39" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="AW22" s="39" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AX22" s="39" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="AY22" s="39" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="AZ22" s="39" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA22" s="39" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="BB22" s="39" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="BC22" s="39" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="BD22" s="39" t="s"/>
+      <x:c r="BE22" s="39" t="s"/>
+      <x:c r="BF22" s="40" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="BG22" s="39" t="s"/>
+      <x:c r="BH22" s="39" t="s"/>
+      <x:c r="BI22" s="39" t="s"/>
+      <x:c r="BJ22" s="39" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A23" s="42" t="s"/>
+      <x:c r="B23" s="38" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C23" s="39" t="s"/>
+      <x:c r="D23" s="39" t="s"/>
+      <x:c r="E23" s="39" t="s"/>
+      <x:c r="F23" s="39" t="s"/>
+      <x:c r="G23" s="39" t="s"/>
+      <x:c r="H23" s="39" t="s"/>
+      <x:c r="I23" s="39" t="s"/>
+      <x:c r="J23" s="39" t="s"/>
+      <x:c r="K23" s="39" t="s"/>
+      <x:c r="L23" s="39" t="s"/>
+      <x:c r="M23" s="39" t="s"/>
+      <x:c r="N23" s="39" t="s"/>
+      <x:c r="O23" s="39" t="s"/>
+      <x:c r="P23" s="39" t="s"/>
+      <x:c r="Q23" s="39" t="s"/>
+      <x:c r="R23" s="39" t="s"/>
+      <x:c r="S23" s="39" t="s"/>
+      <x:c r="T23" s="39" t="s"/>
+      <x:c r="U23" s="39" t="s"/>
+      <x:c r="V23" s="39" t="s"/>
+      <x:c r="W23" s="39" t="s"/>
+      <x:c r="X23" s="39" t="s"/>
+      <x:c r="Y23" s="39" t="s"/>
+      <x:c r="Z23" s="39" t="s"/>
+      <x:c r="AA23" s="39" t="s"/>
+      <x:c r="AB23" s="39" t="s"/>
+      <x:c r="AC23" s="39" t="s"/>
+      <x:c r="AD23" s="39" t="s"/>
+      <x:c r="AE23" s="39" t="s"/>
+      <x:c r="AF23" s="39" t="s"/>
+      <x:c r="AG23" s="39" t="s"/>
+      <x:c r="AH23" s="39" t="s"/>
+      <x:c r="AI23" s="39" t="s"/>
+      <x:c r="AJ23" s="39" t="s"/>
+      <x:c r="AK23" s="39" t="s"/>
+      <x:c r="AL23" s="39" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AM23" s="39" t="s"/>
+      <x:c r="AN23" s="39" t="s"/>
+      <x:c r="AO23" s="39" t="s"/>
+      <x:c r="AP23" s="39" t="s"/>
+      <x:c r="AQ23" s="39" t="s"/>
+      <x:c r="AR23" s="39" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="AS23" s="39" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="AT23" s="39" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="AU23" s="39" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="AV23" s="39" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AW23" s="39" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="AX23" s="39" t="s"/>
+      <x:c r="AY23" s="39" t="s"/>
+      <x:c r="AZ23" s="39" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA23" s="39" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BB23" s="39" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="BC23" s="39" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="BD23" s="39" t="s"/>
+      <x:c r="BE23" s="39" t="s"/>
+      <x:c r="BF23" s="39" t="s"/>
+      <x:c r="BG23" s="39" t="s"/>
+      <x:c r="BH23" s="39" t="s"/>
+      <x:c r="BI23" s="39" t="s"/>
+      <x:c r="BJ23" s="39" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:62" ht="76.5" customHeight="1">
+      <x:c r="A24" s="43" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B24" s="36" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C24" s="44" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D24" s="44" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="E24" s="44" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F24" s="44" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G24" s="44" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H24" s="44" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="I24" s="44" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="J24" s="44" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="K24" s="44" t="s"/>
+      <x:c r="L24" s="44" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="M24" s="44" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N24" s="44" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="O24" s="44" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="P24" s="44" t="s"/>
+      <x:c r="Q24" s="44" t="s"/>
+      <x:c r="R24" s="44" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="S24" s="44" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="T24" s="44" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="U24" s="44" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="V24" s="44" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="W24" s="44" t="s"/>
+      <x:c r="X24" s="44" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="Y24" s="44" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="Z24" s="44" t="s"/>
+      <x:c r="AA24" s="44" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="AB24" s="44" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="AC24" s="44" t="s"/>
+      <x:c r="AD24" s="44" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="AE24" s="44" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AF24" s="44" t="s"/>
+      <x:c r="AG24" s="44" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="AH24" s="44" t="s"/>
+      <x:c r="AI24" s="44" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="AJ24" s="44" t="s"/>
+      <x:c r="AK24" s="44" t="s"/>
+      <x:c r="AL24" s="45" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="AM24" s="44" t="s"/>
+      <x:c r="AN24" s="44" t="s"/>
+      <x:c r="AO24" s="44" t="s"/>
+      <x:c r="AP24" s="44" t="s"/>
+      <x:c r="AQ24" s="44" t="s"/>
+      <x:c r="AR24" s="44" t="s"/>
+      <x:c r="AS24" s="44" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AT24" s="45" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="AU24" s="44" t="s"/>
+      <x:c r="AV24" s="44" t="s"/>
+      <x:c r="AW24" s="44" t="s"/>
+      <x:c r="AX24" s="44" t="s"/>
+      <x:c r="AY24" s="44" t="s"/>
+      <x:c r="AZ24" s="44" t="s"/>
+      <x:c r="BA24" s="44" t="s"/>
+      <x:c r="BB24" s="44" t="s"/>
+      <x:c r="BC24" s="44" t="s"/>
+      <x:c r="BD24" s="44" t="s"/>
+      <x:c r="BE24" s="44" t="s"/>
+      <x:c r="BF24" s="44" t="s"/>
+      <x:c r="BG24" s="44" t="s"/>
+      <x:c r="BH24" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI24" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BJ24" s="44" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:62" ht="63.75" customHeight="1">
+      <x:c r="A25" s="46" t="s"/>
+      <x:c r="B25" s="36" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C25" s="44" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D25" s="44" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E25" s="44" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F25" s="44" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G25" s="44" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H25" s="44" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I25" s="44" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J25" s="44" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="K25" s="44" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="L25" s="44" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="M25" s="44" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="N25" s="44" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="O25" s="44" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="P25" s="44" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="Q25" s="44" t="s"/>
+      <x:c r="R25" s="44" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="S25" s="44" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="T25" s="44" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="U25" s="44" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="V25" s="44" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="W25" s="44" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="X25" s="44" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="Y25" s="44" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="Z25" s="44" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="AA25" s="44" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="AB25" s="44" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="AC25" s="44" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="AD25" s="44" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="AE25" s="44" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="AF25" s="44" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="AG25" s="44" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="AH25" s="44" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="AI25" s="44" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="AJ25" s="45" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="AK25" s="44" t="s"/>
+      <x:c r="AL25" s="44" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="AM25" s="44" t="s"/>
+      <x:c r="AN25" s="44" t="s"/>
+      <x:c r="AO25" s="44" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="AP25" s="44" t="s"/>
+      <x:c r="AQ25" s="44" t="s"/>
+      <x:c r="AR25" s="44" t="s"/>
+      <x:c r="AS25" s="44" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="AT25" s="44" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AU25" s="44" t="s"/>
+      <x:c r="AV25" s="44" t="s"/>
+      <x:c r="AW25" s="44" t="s"/>
+      <x:c r="AX25" s="44" t="s"/>
+      <x:c r="AY25" s="44" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AZ25" s="44" t="s"/>
+      <x:c r="BA25" s="44" t="s"/>
+      <x:c r="BB25" s="44" t="s"/>
+      <x:c r="BC25" s="44" t="s"/>
+      <x:c r="BD25" s="44" t="s"/>
+      <x:c r="BE25" s="44" t="s"/>
+      <x:c r="BF25" s="44" t="s"/>
+      <x:c r="BG25" s="44" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BH25" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI25" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BJ25" s="44" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A26" s="46" t="s"/>
+      <x:c r="B26" s="36" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C26" s="44" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="D26" s="44" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="E26" s="44" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F26" s="44" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G26" s="44" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H26" s="44" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="I26" s="44" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="J26" s="44" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K26" s="44" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="L26" s="44" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="M26" s="44" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="N26" s="44" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="O26" s="44" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="P26" s="44" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q26" s="44" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="R26" s="44" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="S26" s="44" t="s"/>
+      <x:c r="T26" s="44" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="U26" s="44" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="V26" s="44" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="W26" s="44" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="X26" s="44" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="Y26" s="44" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="Z26" s="44" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="AA26" s="44" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="AB26" s="44" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="AC26" s="44" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="AD26" s="44" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="AE26" s="44" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="AF26" s="44" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="AG26" s="44" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="AH26" s="44" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="AI26" s="44" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="AJ26" s="44" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="AK26" s="44" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="AL26" s="44" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="AM26" s="44" t="s"/>
+      <x:c r="AN26" s="44" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="AO26" s="44" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AP26" s="44" t="s"/>
+      <x:c r="AQ26" s="44" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="AR26" s="44" t="s"/>
+      <x:c r="AS26" s="44" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="AT26" s="44" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="AU26" s="44" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AV26" s="44" t="s"/>
+      <x:c r="AW26" s="44" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="AX26" s="44" t="s"/>
+      <x:c r="AY26" s="44" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="AZ26" s="44" t="s"/>
+      <x:c r="BA26" s="44" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="BB26" s="45" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="BC26" s="44" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="BD26" s="44" t="s"/>
+      <x:c r="BE26" s="44" t="s"/>
+      <x:c r="BF26" s="44" t="s"/>
+      <x:c r="BG26" s="44" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BH26" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI26" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BJ26" s="44" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A27" s="46" t="s"/>
+      <x:c r="B27" s="36" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C27" s="44" t="s"/>
+      <x:c r="D27" s="44" t="s"/>
+      <x:c r="E27" s="44" t="s"/>
+      <x:c r="F27" s="44" t="s"/>
+      <x:c r="G27" s="44" t="s"/>
+      <x:c r="H27" s="44" t="s"/>
+      <x:c r="I27" s="44" t="s"/>
+      <x:c r="J27" s="44" t="s"/>
+      <x:c r="K27" s="44" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="L27" s="44" t="s"/>
+      <x:c r="M27" s="44" t="s"/>
+      <x:c r="N27" s="44" t="s"/>
+      <x:c r="O27" s="44" t="s"/>
+      <x:c r="P27" s="44" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="Q27" s="44" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="R27" s="44" t="s"/>
+      <x:c r="S27" s="44" t="s"/>
+      <x:c r="T27" s="44" t="s"/>
+      <x:c r="U27" s="44" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="V27" s="44" t="s"/>
+      <x:c r="W27" s="44" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="X27" s="44" t="s"/>
+      <x:c r="Y27" s="44" t="s"/>
+      <x:c r="Z27" s="44" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="AA27" s="44" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AB27" s="45" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="AC27" s="44" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="AD27" s="44" t="s"/>
+      <x:c r="AE27" s="44" t="s"/>
+      <x:c r="AF27" s="44" t="s"/>
+      <x:c r="AG27" s="44" t="s"/>
+      <x:c r="AH27" s="44" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="AI27" s="44" t="s"/>
+      <x:c r="AJ27" s="44" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="AK27" s="44" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="AL27" s="44" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="AM27" s="44" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="AN27" s="44" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="AO27" s="44" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="AP27" s="44" t="s"/>
+      <x:c r="AQ27" s="44" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="AR27" s="44" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="AS27" s="44" t="s"/>
+      <x:c r="AT27" s="44" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="AU27" s="44" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="AV27" s="44" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="AW27" s="44" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="AX27" s="44" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="AY27" s="44" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="AZ27" s="44" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA27" s="44" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="BB27" s="44" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="BC27" s="44" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="BD27" s="44" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="BE27" s="44" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="BF27" s="44" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="BG27" s="44" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="BH27" s="44" t="s"/>
+      <x:c r="BI27" s="44" t="s"/>
+      <x:c r="BJ27" s="44" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A28" s="46" t="s"/>
+      <x:c r="B28" s="36" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C28" s="44" t="s"/>
+      <x:c r="D28" s="44" t="s"/>
+      <x:c r="E28" s="44" t="s"/>
+      <x:c r="F28" s="44" t="s"/>
+      <x:c r="G28" s="44" t="s"/>
+      <x:c r="H28" s="44" t="s"/>
+      <x:c r="I28" s="44" t="s"/>
+      <x:c r="J28" s="44" t="s"/>
+      <x:c r="K28" s="44" t="s"/>
+      <x:c r="L28" s="44" t="s"/>
+      <x:c r="M28" s="44" t="s"/>
+      <x:c r="N28" s="44" t="s"/>
+      <x:c r="O28" s="44" t="s"/>
+      <x:c r="P28" s="44" t="s"/>
+      <x:c r="Q28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="R28" s="44" t="s"/>
+      <x:c r="S28" s="44" t="s"/>
+      <x:c r="T28" s="44" t="s"/>
+      <x:c r="U28" s="44" t="s"/>
+      <x:c r="V28" s="44" t="s"/>
+      <x:c r="W28" s="44" t="s"/>
+      <x:c r="X28" s="44" t="s"/>
+      <x:c r="Y28" s="44" t="s"/>
+      <x:c r="Z28" s="44" t="s"/>
+      <x:c r="AA28" s="44" t="s"/>
+      <x:c r="AB28" s="44" t="s"/>
+      <x:c r="AC28" s="44" t="s"/>
+      <x:c r="AD28" s="44" t="s"/>
+      <x:c r="AE28" s="44" t="s"/>
+      <x:c r="AF28" s="44" t="s"/>
+      <x:c r="AG28" s="44" t="s"/>
+      <x:c r="AH28" s="44" t="s"/>
+      <x:c r="AI28" s="44" t="s"/>
+      <x:c r="AJ28" s="44" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AK28" s="44" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="AL28" s="44" t="s"/>
+      <x:c r="AM28" s="44" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="AN28" s="44" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="AO28" s="44" t="s"/>
+      <x:c r="AP28" s="44" t="s"/>
+      <x:c r="AQ28" s="44" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="AR28" s="44" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="AS28" s="44" t="s"/>
+      <x:c r="AT28" s="44" t="s"/>
+      <x:c r="AU28" s="44" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="AV28" s="44" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="AW28" s="44" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="AX28" s="44" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="AY28" s="44" t="s"/>
+      <x:c r="AZ28" s="44" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA28" s="44" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="BB28" s="44" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="BC28" s="44" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="BD28" s="44" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="BE28" s="44" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="BF28" s="44" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="BG28" s="44" t="s"/>
+      <x:c r="BH28" s="44" t="s"/>
+      <x:c r="BI28" s="44" t="s"/>
+      <x:c r="BJ28" s="44" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A29" s="47" t="s"/>
+      <x:c r="B29" s="36" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C29" s="44" t="s"/>
+      <x:c r="D29" s="44" t="s"/>
+      <x:c r="E29" s="44" t="s"/>
+      <x:c r="F29" s="44" t="s"/>
+      <x:c r="G29" s="44" t="s"/>
+      <x:c r="H29" s="44" t="s"/>
+      <x:c r="I29" s="44" t="s"/>
+      <x:c r="J29" s="44" t="s"/>
+      <x:c r="K29" s="44" t="s"/>
+      <x:c r="L29" s="44" t="s"/>
+      <x:c r="M29" s="44" t="s"/>
+      <x:c r="N29" s="44" t="s"/>
+      <x:c r="O29" s="44" t="s"/>
+      <x:c r="P29" s="44" t="s"/>
+      <x:c r="Q29" s="44" t="s"/>
+      <x:c r="R29" s="44" t="s"/>
+      <x:c r="S29" s="44" t="s"/>
+      <x:c r="T29" s="44" t="s"/>
+      <x:c r="U29" s="44" t="s"/>
+      <x:c r="V29" s="44" t="s"/>
+      <x:c r="W29" s="44" t="s"/>
+      <x:c r="X29" s="44" t="s"/>
+      <x:c r="Y29" s="44" t="s"/>
+      <x:c r="Z29" s="44" t="s"/>
+      <x:c r="AA29" s="44" t="s"/>
+      <x:c r="AB29" s="44" t="s"/>
+      <x:c r="AC29" s="44" t="s"/>
+      <x:c r="AD29" s="44" t="s"/>
+      <x:c r="AE29" s="44" t="s"/>
+      <x:c r="AF29" s="44" t="s"/>
+      <x:c r="AG29" s="44" t="s"/>
+      <x:c r="AH29" s="44" t="s"/>
+      <x:c r="AI29" s="44" t="s"/>
+      <x:c r="AJ29" s="44" t="s"/>
+      <x:c r="AK29" s="44" t="s"/>
+      <x:c r="AL29" s="44" t="s"/>
+      <x:c r="AM29" s="44" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="AN29" s="44" t="s"/>
+      <x:c r="AO29" s="44" t="s"/>
+      <x:c r="AP29" s="44" t="s"/>
+      <x:c r="AQ29" s="44" t="s"/>
+      <x:c r="AR29" s="44" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="AS29" s="44" t="s"/>
+      <x:c r="AT29" s="44" t="s"/>
+      <x:c r="AU29" s="44" t="s"/>
+      <x:c r="AV29" s="44" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="AW29" s="44" t="s"/>
+      <x:c r="AX29" s="44" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="AY29" s="44" t="s"/>
+      <x:c r="AZ29" s="44" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA29" s="44" t="s"/>
+      <x:c r="BB29" s="44" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="BC29" s="44" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="BD29" s="44" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="BE29" s="44" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="BF29" s="44" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BG29" s="44" t="s"/>
+      <x:c r="BH29" s="44" t="s"/>
+      <x:c r="BI29" s="44" t="s"/>
+      <x:c r="BJ29" s="44" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A30" s="37" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B30" s="38" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C30" s="39" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D30" s="39" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="E30" s="39" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F30" s="39" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G30" s="39" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H30" s="39" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="I30" s="39" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="J30" s="40" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K30" s="39" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="L30" s="40" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="M30" s="39" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="N30" s="39" t="s"/>
+      <x:c r="O30" s="39" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="P30" s="39" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="Q30" s="39" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="R30" s="39" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="S30" s="39" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="T30" s="39" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="U30" s="39" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="V30" s="39" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="W30" s="39" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="X30" s="39" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="Y30" s="39" t="s"/>
+      <x:c r="Z30" s="39" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="AA30" s="39" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="AB30" s="39" t="s"/>
+      <x:c r="AC30" s="39" t="s"/>
+      <x:c r="AD30" s="40" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="AE30" s="39" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="AF30" s="39" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AG30" s="39" t="s"/>
+      <x:c r="AH30" s="39" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="AI30" s="39" t="s"/>
+      <x:c r="AJ30" s="39" t="s"/>
+      <x:c r="AK30" s="39" t="s"/>
+      <x:c r="AL30" s="39" t="s"/>
+      <x:c r="AM30" s="39" t="s"/>
+      <x:c r="AN30" s="39" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="AO30" s="39" t="s"/>
+      <x:c r="AP30" s="39" t="s"/>
+      <x:c r="AQ30" s="39" t="s"/>
+      <x:c r="AR30" s="39" t="s"/>
+      <x:c r="AS30" s="39" t="s"/>
+      <x:c r="AT30" s="39" t="s"/>
+      <x:c r="AU30" s="39" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="AV30" s="40" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AW30" s="39" t="s"/>
+      <x:c r="AX30" s="39" t="s"/>
+      <x:c r="AY30" s="39" t="s"/>
+      <x:c r="AZ30" s="39" t="s"/>
+      <x:c r="BA30" s="39" t="s"/>
+      <x:c r="BB30" s="39" t="s"/>
+      <x:c r="BC30" s="39" t="s"/>
+      <x:c r="BD30" s="39" t="s"/>
+      <x:c r="BE30" s="39" t="s"/>
+      <x:c r="BF30" s="39" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BG30" s="39" t="s"/>
+      <x:c r="BH30" s="39" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI30" s="39" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BJ30" s="39" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A31" s="41" t="s"/>
+      <x:c r="B31" s="38" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C31" s="39" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D31" s="39" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E31" s="39" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F31" s="39" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G31" s="39" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="H31" s="39" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="I31" s="39" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="J31" s="39" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K31" s="39" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="L31" s="39" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="M31" s="39" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="N31" s="39" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="O31" s="39" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="P31" s="40" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="Q31" s="39" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="R31" s="39" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="S31" s="39" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="T31" s="39" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="U31" s="39" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="V31" s="39" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="W31" s="39" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="X31" s="39" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="Y31" s="39" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="Z31" s="39" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="AA31" s="39" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="AB31" s="39" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="AC31" s="39" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AD31" s="39" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="AE31" s="39" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="AF31" s="39" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AG31" s="39" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="AH31" s="39" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="AI31" s="39" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="AJ31" s="39" t="s"/>
+      <x:c r="AK31" s="39" t="s"/>
+      <x:c r="AL31" s="39" t="s"/>
+      <x:c r="AM31" s="39" t="s"/>
+      <x:c r="AN31" s="39" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="AO31" s="39" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="AP31" s="39" t="s"/>
+      <x:c r="AQ31" s="39" t="s"/>
+      <x:c r="AR31" s="39" t="s"/>
+      <x:c r="AS31" s="39" t="s"/>
+      <x:c r="AT31" s="39" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="AU31" s="39" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="AV31" s="39" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="AW31" s="40" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AX31" s="39" t="s"/>
+      <x:c r="AY31" s="39" t="s"/>
+      <x:c r="AZ31" s="39" t="s"/>
+      <x:c r="BA31" s="39" t="s"/>
+      <x:c r="BB31" s="39" t="s"/>
+      <x:c r="BC31" s="39" t="s"/>
+      <x:c r="BD31" s="39" t="s"/>
+      <x:c r="BE31" s="39" t="s"/>
+      <x:c r="BF31" s="39" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BG31" s="39" t="s"/>
+      <x:c r="BH31" s="39" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI31" s="39" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BJ31" s="39" t="s"/>
+    </x:row>
+    <x:row r="32" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A32" s="41" t="s"/>
+      <x:c r="B32" s="38" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C32" s="39" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D32" s="39" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="E32" s="39" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F32" s="39" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G32" s="39" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H32" s="39" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="I32" s="40" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="J32" s="39" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="K32" s="39" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="L32" s="39" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="M32" s="39" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="N32" s="39" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="O32" s="39" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="P32" s="39" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="Q32" s="39" t="s"/>
+      <x:c r="R32" s="39" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="S32" s="39" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="T32" s="39" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="U32" s="39" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="V32" s="39" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="W32" s="39" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="X32" s="39" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="Y32" s="39" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="Z32" s="39" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="AA32" s="39" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="AB32" s="39" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="AC32" s="39" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="AD32" s="39" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AE32" s="39" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="AF32" s="39" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="AG32" s="39" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="AH32" s="39" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="AI32" s="39" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="AJ32" s="39" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AK32" s="39" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="AL32" s="39" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="AM32" s="39" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AN32" s="39" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="AO32" s="39" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AP32" s="39" t="s"/>
+      <x:c r="AQ32" s="39" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="AR32" s="39" t="s"/>
+      <x:c r="AS32" s="40" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AT32" s="39" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="AU32" s="39" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="AV32" s="39" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="AW32" s="39" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="AX32" s="39" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="AY32" s="39" t="s"/>
+      <x:c r="AZ32" s="40" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="BA32" s="39" t="s"/>
+      <x:c r="BB32" s="39" t="s"/>
+      <x:c r="BC32" s="39" t="s"/>
+      <x:c r="BD32" s="39" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="BE32" s="39" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="BF32" s="39" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="BG32" s="39" t="s"/>
+      <x:c r="BH32" s="39" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI32" s="39" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BJ32" s="39" t="s"/>
+    </x:row>
+    <x:row r="33" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A33" s="41" t="s"/>
+      <x:c r="B33" s="38" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C33" s="39" t="s"/>
+      <x:c r="D33" s="39" t="s"/>
+      <x:c r="E33" s="39" t="s"/>
+      <x:c r="F33" s="39" t="s"/>
+      <x:c r="G33" s="39" t="s"/>
+      <x:c r="H33" s="39" t="s"/>
+      <x:c r="I33" s="39" t="s"/>
+      <x:c r="J33" s="39" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K33" s="39" t="s"/>
+      <x:c r="L33" s="39" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="M33" s="40" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="N33" s="39" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="O33" s="39" t="s"/>
+      <x:c r="P33" s="39" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="Q33" s="39" t="s"/>
+      <x:c r="R33" s="39" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="S33" s="39" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="T33" s="39" t="s"/>
+      <x:c r="U33" s="39" t="s"/>
+      <x:c r="V33" s="39" t="s"/>
+      <x:c r="W33" s="39" t="s"/>
+      <x:c r="X33" s="39" t="s"/>
+      <x:c r="Y33" s="39" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="Z33" s="39" t="s"/>
+      <x:c r="AA33" s="39" t="s"/>
+      <x:c r="AB33" s="39" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="AC33" s="39" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AD33" s="39" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="AE33" s="39" t="s"/>
+      <x:c r="AF33" s="39" t="s"/>
+      <x:c r="AG33" s="39" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AH33" s="39" t="s"/>
+      <x:c r="AI33" s="39" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="AJ33" s="39" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="AK33" s="39" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="AL33" s="39" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="AM33" s="39" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="AN33" s="39" t="s"/>
+      <x:c r="AO33" s="39" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AP33" s="39" t="s"/>
+      <x:c r="AQ33" s="39" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="AR33" s="39" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="AS33" s="39" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="AT33" s="39" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="AU33" s="39" t="s"/>
+      <x:c r="AV33" s="39" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="AW33" s="39" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="AX33" s="39" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="AY33" s="39" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="AZ33" s="39" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA33" s="39" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="BB33" s="39" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="BC33" s="39" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="BD33" s="39" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="BE33" s="39" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="BF33" s="39" t="s"/>
+      <x:c r="BG33" s="39" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BH33" s="39" t="s"/>
+      <x:c r="BI33" s="39" t="s"/>
+      <x:c r="BJ33" s="39" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A34" s="41" t="s"/>
+      <x:c r="B34" s="38" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C34" s="39" t="s"/>
+      <x:c r="D34" s="39" t="s"/>
+      <x:c r="E34" s="39" t="s"/>
+      <x:c r="F34" s="39" t="s"/>
+      <x:c r="G34" s="39" t="s"/>
+      <x:c r="H34" s="39" t="s"/>
+      <x:c r="I34" s="39" t="s"/>
+      <x:c r="J34" s="39" t="s"/>
+      <x:c r="K34" s="39" t="s"/>
+      <x:c r="L34" s="39" t="s"/>
+      <x:c r="M34" s="39" t="s"/>
+      <x:c r="N34" s="39" t="s"/>
+      <x:c r="O34" s="39" t="s"/>
+      <x:c r="P34" s="39" t="s"/>
+      <x:c r="Q34" s="39" t="s"/>
+      <x:c r="R34" s="39" t="s"/>
+      <x:c r="S34" s="39" t="s"/>
+      <x:c r="T34" s="39" t="s"/>
+      <x:c r="U34" s="39" t="s"/>
+      <x:c r="V34" s="39" t="s"/>
+      <x:c r="W34" s="39" t="s"/>
+      <x:c r="X34" s="39" t="s"/>
+      <x:c r="Y34" s="39" t="s"/>
+      <x:c r="Z34" s="39" t="s"/>
+      <x:c r="AA34" s="39" t="s"/>
+      <x:c r="AB34" s="39" t="s"/>
+      <x:c r="AC34" s="39" t="s"/>
+      <x:c r="AD34" s="39" t="s"/>
+      <x:c r="AE34" s="39" t="s"/>
+      <x:c r="AF34" s="39" t="s"/>
+      <x:c r="AG34" s="39" t="s"/>
+      <x:c r="AH34" s="39" t="s"/>
+      <x:c r="AI34" s="39" t="s"/>
+      <x:c r="AJ34" s="39" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="AK34" s="39" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="AL34" s="39" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AM34" s="39" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AN34" s="39" t="s"/>
+      <x:c r="AO34" s="39" t="s"/>
+      <x:c r="AP34" s="39" t="s"/>
+      <x:c r="AQ34" s="39" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="AR34" s="39" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="AS34" s="39" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="AT34" s="39" t="s"/>
+      <x:c r="AU34" s="39" t="s"/>
+      <x:c r="AV34" s="39" t="s"/>
+      <x:c r="AW34" s="39" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="AX34" s="39" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="AY34" s="39" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="AZ34" s="39" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA34" s="39" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="BB34" s="39" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="BC34" s="39" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="BD34" s="39" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="BE34" s="39" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="BF34" s="39" t="s"/>
+      <x:c r="BG34" s="39" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BH34" s="39" t="s"/>
+      <x:c r="BI34" s="39" t="s"/>
+      <x:c r="BJ34" s="39" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A35" s="42" t="s"/>
+      <x:c r="B35" s="38" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C35" s="39" t="s"/>
+      <x:c r="D35" s="39" t="s"/>
+      <x:c r="E35" s="39" t="s"/>
+      <x:c r="F35" s="39" t="s"/>
+      <x:c r="G35" s="39" t="s"/>
+      <x:c r="H35" s="39" t="s"/>
+      <x:c r="I35" s="39" t="s"/>
+      <x:c r="J35" s="39" t="s"/>
+      <x:c r="K35" s="39" t="s"/>
+      <x:c r="L35" s="39" t="s"/>
+      <x:c r="M35" s="39" t="s"/>
+      <x:c r="N35" s="39" t="s"/>
+      <x:c r="O35" s="39" t="s"/>
+      <x:c r="P35" s="39" t="s"/>
+      <x:c r="Q35" s="39" t="s"/>
+      <x:c r="R35" s="39" t="s"/>
+      <x:c r="S35" s="39" t="s"/>
+      <x:c r="T35" s="39" t="s"/>
+      <x:c r="U35" s="39" t="s"/>
+      <x:c r="V35" s="39" t="s"/>
+      <x:c r="W35" s="39" t="s"/>
+      <x:c r="X35" s="39" t="s"/>
+      <x:c r="Y35" s="39" t="s"/>
+      <x:c r="Z35" s="39" t="s"/>
+      <x:c r="AA35" s="39" t="s"/>
+      <x:c r="AB35" s="39" t="s"/>
+      <x:c r="AC35" s="39" t="s"/>
+      <x:c r="AD35" s="39" t="s"/>
+      <x:c r="AE35" s="39" t="s"/>
+      <x:c r="AF35" s="39" t="s"/>
+      <x:c r="AG35" s="39" t="s"/>
+      <x:c r="AH35" s="39" t="s"/>
+      <x:c r="AI35" s="39" t="s"/>
+      <x:c r="AJ35" s="39" t="s"/>
+      <x:c r="AK35" s="39" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AL35" s="39" t="s"/>
+      <x:c r="AM35" s="39" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AN35" s="39" t="s"/>
+      <x:c r="AO35" s="39" t="s"/>
+      <x:c r="AP35" s="39" t="s"/>
+      <x:c r="AQ35" s="40" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="AR35" s="39" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="AS35" s="39" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="AT35" s="39" t="s"/>
+      <x:c r="AU35" s="39" t="s"/>
+      <x:c r="AV35" s="39" t="s"/>
+      <x:c r="AW35" s="39" t="s"/>
+      <x:c r="AX35" s="39" t="s"/>
+      <x:c r="AY35" s="39" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="AZ35" s="39" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA35" s="39" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="BB35" s="39" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="BC35" s="39" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="BD35" s="39" t="s"/>
+      <x:c r="BE35" s="39" t="s"/>
+      <x:c r="BF35" s="39" t="s"/>
+      <x:c r="BG35" s="39" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BH35" s="39" t="s"/>
+      <x:c r="BI35" s="39" t="s"/>
+      <x:c r="BJ35" s="39" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:62" ht="76.5" customHeight="1">
+      <x:c r="A36" s="43" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B36" s="36" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C36" s="44" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D36" s="44" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="E36" s="44" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F36" s="44" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G36" s="44" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="H36" s="44" t="s"/>
+      <x:c r="I36" s="44" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J36" s="44" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="K36" s="44" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="L36" s="44" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="M36" s="44" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="N36" s="44" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="O36" s="44" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="P36" s="44" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="Q36" s="44" t="s"/>
+      <x:c r="R36" s="44" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="S36" s="44" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="T36" s="44" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="U36" s="44" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="V36" s="44" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="W36" s="44" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="X36" s="44" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="Y36" s="44" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="Z36" s="44" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="AA36" s="44" t="s"/>
+      <x:c r="AB36" s="44" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="AC36" s="44" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="AD21" s="38" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="AE21" s="38" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="AF21" s="38" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="AG21" s="38" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="AH21" s="38" t="s">
+      <x:c r="AD36" s="44" t="s"/>
+      <x:c r="AE36" s="44" t="s"/>
+      <x:c r="AF36" s="44" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="AG36" s="44" t="s"/>
+      <x:c r="AH36" s="44" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="AI21" s="38" t="s"/>
-      <x:c r="AJ21" s="38" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="AK21" s="38" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="AL21" s="38" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="AM21" s="38" t="s">
+      <x:c r="AI36" s="44" t="s"/>
+      <x:c r="AJ36" s="44" t="s"/>
+      <x:c r="AK36" s="44" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AL36" s="44" t="s"/>
+      <x:c r="AM36" s="44" t="s"/>
+      <x:c r="AN36" s="44" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="AO36" s="44" t="s"/>
+      <x:c r="AP36" s="44" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="AQ36" s="44" t="s"/>
+      <x:c r="AR36" s="44" t="s"/>
+      <x:c r="AS36" s="44" t="s"/>
+      <x:c r="AT36" s="44" t="s"/>
+      <x:c r="AU36" s="44" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="AV36" s="44" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="AW36" s="44" t="s"/>
+      <x:c r="AX36" s="44" t="s"/>
+      <x:c r="AY36" s="44" t="s"/>
+      <x:c r="AZ36" s="44" t="s"/>
+      <x:c r="BA36" s="44" t="s"/>
+      <x:c r="BB36" s="44" t="s"/>
+      <x:c r="BC36" s="44" t="s"/>
+      <x:c r="BD36" s="44" t="s"/>
+      <x:c r="BE36" s="44" t="s"/>
+      <x:c r="BF36" s="44" t="s"/>
+      <x:c r="BG36" s="44" t="s"/>
+      <x:c r="BH36" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI36" s="44" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="BJ36" s="44" t="s"/>
+    </x:row>
+    <x:row r="37" spans="1:62" ht="63.75" customHeight="1">
+      <x:c r="A37" s="46" t="s"/>
+      <x:c r="B37" s="36" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C37" s="44" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D37" s="44" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="E37" s="44" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="F37" s="44" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G37" s="44" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H37" s="44" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I37" s="44" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="J37" s="44" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K37" s="44" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="L37" s="44" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="M37" s="44" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="N37" s="44" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="O37" s="44" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="P37" s="44" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="Q37" s="44" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="R37" s="44" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="S37" s="44" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="T37" s="44" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="U37" s="44" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="V37" s="44" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="W37" s="44" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="X37" s="44" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="Y37" s="44" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="Z37" s="44" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="AA37" s="44" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="AB37" s="44" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="AC37" s="44" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="AD37" s="44" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="AE37" s="44" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="AF37" s="44" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="AG37" s="44" t="s"/>
+      <x:c r="AH37" s="44" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="AI37" s="44" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="AJ37" s="44" t="s"/>
+      <x:c r="AK37" s="44" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AL37" s="44" t="s"/>
+      <x:c r="AM37" s="44" t="s"/>
+      <x:c r="AN37" s="44" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="AO37" s="44" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="AP37" s="44" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="AQ37" s="44" t="s"/>
+      <x:c r="AR37" s="44" t="s"/>
+      <x:c r="AS37" s="44" t="s"/>
+      <x:c r="AT37" s="44" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="AU37" s="44" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="AV37" s="44" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="AW37" s="44" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="AX37" s="44" t="s"/>
+      <x:c r="AY37" s="44" t="s"/>
+      <x:c r="AZ37" s="44" t="s"/>
+      <x:c r="BA37" s="44" t="s"/>
+      <x:c r="BB37" s="44" t="s"/>
+      <x:c r="BC37" s="44" t="s"/>
+      <x:c r="BD37" s="44" t="s"/>
+      <x:c r="BE37" s="44" t="s"/>
+      <x:c r="BF37" s="44" t="s"/>
+      <x:c r="BG37" s="44" t="s"/>
+      <x:c r="BH37" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI37" s="44" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="BJ37" s="44" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:62" ht="76.5" customHeight="1">
+      <x:c r="A38" s="46" t="s"/>
+      <x:c r="B38" s="36" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C38" s="44" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="D38" s="44" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="E38" s="44" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F38" s="44" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="G38" s="44" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H38" s="44" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I38" s="44" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="J38" s="44" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="K38" s="44" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="L38" s="44" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="M38" s="44" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N38" s="44" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="O38" s="44" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="P38" s="44" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="Q38" s="44" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="R38" s="44" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="S38" s="44" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="T38" s="44" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="U38" s="44" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="V38" s="44" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="W38" s="44" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="X38" s="44" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="Y38" s="44" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="Z38" s="44" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="AA38" s="44" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="AB38" s="44" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AC38" s="44" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="AD38" s="44" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="AE38" s="44" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="AF38" s="44" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="AG38" s="44" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="AH38" s="44" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="AI38" s="44" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="AJ38" s="44" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="AK38" s="44" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="AN21" s="38" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="AO21" s="38" t="s">
+      <x:c r="AL38" s="44" t="s"/>
+      <x:c r="AM38" s="44" t="s"/>
+      <x:c r="AN38" s="44" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="AO38" s="44" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="AP38" s="44" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="AQ38" s="44" t="s"/>
+      <x:c r="AR38" s="44" t="s"/>
+      <x:c r="AS38" s="44" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="AT38" s="44" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="AU38" s="44" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="AV38" s="44" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="AW38" s="44" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="AX38" s="44" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="AY38" s="44" t="s"/>
+      <x:c r="AZ38" s="44" t="s"/>
+      <x:c r="BA38" s="44" t="s"/>
+      <x:c r="BB38" s="44" t="s"/>
+      <x:c r="BC38" s="44" t="s"/>
+      <x:c r="BD38" s="44" t="s"/>
+      <x:c r="BE38" s="44" t="s"/>
+      <x:c r="BF38" s="44" t="s"/>
+      <x:c r="BG38" s="44" t="s"/>
+      <x:c r="BH38" s="44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="BI38" s="44" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="BJ38" s="44" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A39" s="46" t="s"/>
+      <x:c r="B39" s="36" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C39" s="44" t="s"/>
+      <x:c r="D39" s="44" t="s"/>
+      <x:c r="E39" s="44" t="s"/>
+      <x:c r="F39" s="44" t="s"/>
+      <x:c r="G39" s="44" t="s"/>
+      <x:c r="H39" s="44" t="s"/>
+      <x:c r="I39" s="44" t="s"/>
+      <x:c r="J39" s="44" t="s"/>
+      <x:c r="K39" s="44" t="s"/>
+      <x:c r="L39" s="44" t="s"/>
+      <x:c r="M39" s="44" t="s"/>
+      <x:c r="N39" s="44" t="s"/>
+      <x:c r="O39" s="44" t="s"/>
+      <x:c r="P39" s="44" t="s"/>
+      <x:c r="Q39" s="44" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="R39" s="44" t="s"/>
+      <x:c r="S39" s="44" t="s"/>
+      <x:c r="T39" s="44" t="s"/>
+      <x:c r="U39" s="44" t="s"/>
+      <x:c r="V39" s="44" t="s"/>
+      <x:c r="W39" s="44" t="s"/>
+      <x:c r="X39" s="44" t="s"/>
+      <x:c r="Y39" s="44" t="s"/>
+      <x:c r="Z39" s="44" t="s"/>
+      <x:c r="AA39" s="44" t="s"/>
+      <x:c r="AB39" s="44" t="s"/>
+      <x:c r="AC39" s="44" t="s"/>
+      <x:c r="AD39" s="44" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AP21" s="38" t="s"/>
-      <x:c r="AQ21" s="38" t="s"/>
-      <x:c r="AR21" s="38" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="AS21" s="38" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="AT21" s="38" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="AU21" s="38" t="s">
+      <x:c r="AE39" s="44" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="AF39" s="44" t="s"/>
+      <x:c r="AG39" s="44" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AH39" s="44" t="s"/>
+      <x:c r="AI39" s="44" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="AJ39" s="44" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AK39" s="44" t="s"/>
+      <x:c r="AL39" s="44" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AM39" s="44" t="s"/>
+      <x:c r="AN39" s="44" t="s"/>
+      <x:c r="AO39" s="44" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="AP39" s="44" t="s"/>
+      <x:c r="AQ39" s="44" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="AR39" s="44" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="AS39" s="44" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="AT39" s="44" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="AV21" s="38" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="AW21" s="38" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="AX21" s="38" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="AY21" s="38" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AZ21" s="38" t="s">
+      <x:c r="AU39" s="44" t="s"/>
+      <x:c r="AV39" s="44" t="s"/>
+      <x:c r="AW39" s="44" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="AX39" s="44" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="AY39" s="44" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="AZ39" s="44" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="BA21" s="38" t="s">
+      <x:c r="BA39" s="44" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="BB21" s="38" t="s">
+      <x:c r="BB39" s="44" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="BC39" s="44" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="BC21" s="38" t="s">
+      <x:c r="BD39" s="44" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="BE39" s="44" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="BF39" s="44" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BG39" s="44" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="BH39" s="44" t="s"/>
+      <x:c r="BI39" s="44" t="s"/>
+      <x:c r="BJ39" s="44" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A40" s="46" t="s"/>
+      <x:c r="B40" s="36" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C40" s="44" t="s"/>
+      <x:c r="D40" s="44" t="s"/>
+      <x:c r="E40" s="44" t="s"/>
+      <x:c r="F40" s="44" t="s"/>
+      <x:c r="G40" s="44" t="s"/>
+      <x:c r="H40" s="44" t="s"/>
+      <x:c r="I40" s="44" t="s"/>
+      <x:c r="J40" s="44" t="s"/>
+      <x:c r="K40" s="44" t="s"/>
+      <x:c r="L40" s="44" t="s"/>
+      <x:c r="M40" s="44" t="s"/>
+      <x:c r="N40" s="44" t="s"/>
+      <x:c r="O40" s="44" t="s"/>
+      <x:c r="P40" s="44" t="s"/>
+      <x:c r="Q40" s="44" t="s"/>
+      <x:c r="R40" s="44" t="s"/>
+      <x:c r="S40" s="44" t="s"/>
+      <x:c r="T40" s="44" t="s"/>
+      <x:c r="U40" s="44" t="s"/>
+      <x:c r="V40" s="44" t="s"/>
+      <x:c r="W40" s="44" t="s"/>
+      <x:c r="X40" s="44" t="s"/>
+      <x:c r="Y40" s="44" t="s"/>
+      <x:c r="Z40" s="44" t="s"/>
+      <x:c r="AA40" s="44" t="s"/>
+      <x:c r="AB40" s="44" t="s"/>
+      <x:c r="AC40" s="44" t="s"/>
+      <x:c r="AD40" s="44" t="s"/>
+      <x:c r="AE40" s="44" t="s"/>
+      <x:c r="AF40" s="44" t="s"/>
+      <x:c r="AG40" s="44" t="s"/>
+      <x:c r="AH40" s="44" t="s"/>
+      <x:c r="AI40" s="44" t="s"/>
+      <x:c r="AJ40" s="44" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AK40" s="44" t="s"/>
+      <x:c r="AL40" s="44" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="AM40" s="44" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="AN40" s="44" t="s"/>
+      <x:c r="AO40" s="44" t="s"/>
+      <x:c r="AP40" s="44" t="s"/>
+      <x:c r="AQ40" s="44" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="AR40" s="44" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="AS40" s="44" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="AT40" s="44" t="s"/>
+      <x:c r="AU40" s="44" t="s"/>
+      <x:c r="AV40" s="44" t="s"/>
+      <x:c r="AW40" s="44" t="s"/>
+      <x:c r="AX40" s="44" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AY40" s="44" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="AZ40" s="44" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="BA40" s="44" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="BB40" s="44" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="BC40" s="44" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="BD21" s="38" t="s"/>
-      <x:c r="BE21" s="38" t="s"/>
-      <x:c r="BF21" s="38" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="BG21" s="39" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="BH21" s="38" t="s"/>
-      <x:c r="BI21" s="38" t="s"/>
-      <x:c r="BJ21" s="38" t="s"/>
+      <x:c r="BD40" s="44" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="BE40" s="44" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="BF40" s="44" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BG40" s="44" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="BH40" s="44" t="s"/>
+      <x:c r="BI40" s="44" t="s"/>
+      <x:c r="BJ40" s="44" t="s">
+        <x:v>98</x:v>
+      </x:c>
     </x:row>
-    <x:row r="22" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A22" s="40" t="s"/>
-      <x:c r="B22" s="36" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="C22" s="38" t="s"/>
-      <x:c r="D22" s="38" t="s"/>
-      <x:c r="E22" s="38" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F22" s="38" t="s"/>
-      <x:c r="G22" s="38" t="s"/>
-      <x:c r="H22" s="38" t="s"/>
-      <x:c r="I22" s="38" t="s"/>
-      <x:c r="J22" s="38" t="s"/>
-      <x:c r="K22" s="38" t="s"/>
-      <x:c r="L22" s="38" t="s"/>
-      <x:c r="M22" s="38" t="s"/>
-      <x:c r="N22" s="38" t="s"/>
-      <x:c r="O22" s="38" t="s"/>
-      <x:c r="P22" s="38" t="s"/>
-      <x:c r="Q22" s="38" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="R22" s="38" t="s"/>
-      <x:c r="S22" s="38" t="s"/>
-      <x:c r="T22" s="38" t="s"/>
-      <x:c r="U22" s="38" t="s"/>
-      <x:c r="V22" s="38" t="s"/>
-      <x:c r="W22" s="38" t="s"/>
-      <x:c r="X22" s="38" t="s"/>
-      <x:c r="Y22" s="38" t="s"/>
-      <x:c r="Z22" s="38" t="s"/>
-      <x:c r="AA22" s="38" t="s"/>
-      <x:c r="AB22" s="38" t="s"/>
-      <x:c r="AC22" s="38" t="s"/>
-      <x:c r="AD22" s="38" t="s"/>
-      <x:c r="AE22" s="38" t="s"/>
-      <x:c r="AF22" s="38" t="s"/>
-      <x:c r="AG22" s="38" t="s"/>
-      <x:c r="AH22" s="38" t="s"/>
-      <x:c r="AI22" s="38" t="s"/>
-      <x:c r="AJ22" s="38" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AK22" s="38" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="AL22" s="38" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="AM22" s="38" t="s"/>
-      <x:c r="AN22" s="38" t="s"/>
-      <x:c r="AO22" s="38" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="AP22" s="38" t="s"/>
-      <x:c r="AQ22" s="38" t="s"/>
-      <x:c r="AR22" s="38" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="AS22" s="38" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AT22" s="38" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="AU22" s="38" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="AV22" s="38" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="AW22" s="38" t="s">
+    <x:row r="41" spans="1:62" ht="53.45" customHeight="1">
+      <x:c r="A41" s="47" t="s"/>
+      <x:c r="B41" s="36" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C41" s="44" t="s"/>
+      <x:c r="D41" s="44" t="s"/>
+      <x:c r="E41" s="44" t="s"/>
+      <x:c r="F41" s="44" t="s"/>
+      <x:c r="G41" s="44" t="s"/>
+      <x:c r="H41" s="44" t="s"/>
+      <x:c r="I41" s="44" t="s"/>
+      <x:c r="J41" s="44" t="s"/>
+      <x:c r="K41" s="44" t="s"/>
+      <x:c r="L41" s="44" t="s"/>
+      <x:c r="M41" s="44" t="s"/>
+      <x:c r="N41" s="44" t="s"/>
+      <x:c r="O41" s="44" t="s"/>
+      <x:c r="P41" s="44" t="s"/>
+      <x:c r="Q41" s="44" t="s"/>
+      <x:c r="R41" s="44" t="s"/>
+      <x:c r="S41" s="44" t="s"/>
+      <x:c r="T41" s="44" t="s"/>
+      <x:c r="U41" s="44" t="s"/>
+      <x:c r="V41" s="44" t="s"/>
+      <x:c r="W41" s="44" t="s"/>
+      <x:c r="X41" s="44" t="s"/>
+      <x:c r="Y41" s="44" t="s"/>
+      <x:c r="Z41" s="44" t="s"/>
+      <x:c r="AA41" s="44" t="s"/>
+      <x:c r="AB41" s="44" t="s"/>
+      <x:c r="AC41" s="44" t="s"/>
+      <x:c r="AD41" s="44" t="s"/>
+      <x:c r="AE41" s="44" t="s"/>
+      <x:c r="AF41" s="44" t="s"/>
+      <x:c r="AG41" s="44" t="s"/>
+      <x:c r="AH41" s="44" t="s"/>
+      <x:c r="AI41" s="44" t="s"/>
+      <x:c r="AJ41" s="44" t="s"/>
+      <x:c r="AK41" s="44" t="s"/>
+      <x:c r="AL41" s="44" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="AM41" s="44" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AN41" s="44" t="s"/>
+      <x:c r="AO41" s="44" t="s"/>
+      <x:c r="AP41" s="44" t="s"/>
+      <x:c r="AQ41" s="44" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="AR41" s="44" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="AS41" s="44" t="s"/>
+      <x:c r="AT41" s="44" t="s"/>
+      <x:c r="AU41" s="44" t="s"/>
+      <x:c r="AV41" s="44" t="s"/>
+      <x:c r="AW41" s="44" t="s"/>
+      <x:c r="AX41" s="44" t="s"/>
+      <x:c r="AY41" s="44" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AX22" s="38" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="AY22" s="38" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="AZ22" s="38" t="s">
+      <x:c r="AZ41" s="44" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="BA22" s="38" t="s">
+      <x:c r="BA41" s="44" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="BB22" s="38" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="BC22" s="38" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="BD22" s="38" t="s"/>
-      <x:c r="BE22" s="38" t="s"/>
-      <x:c r="BF22" s="39" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="BG22" s="38" t="s"/>
-      <x:c r="BH22" s="38" t="s"/>
-      <x:c r="BI22" s="38" t="s"/>
-      <x:c r="BJ22" s="38" t="s">
-        <x:v>214</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A23" s="42" t="s"/>
-      <x:c r="B23" s="36" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="C23" s="38" t="s"/>
-      <x:c r="D23" s="38" t="s"/>
-      <x:c r="E23" s="38" t="s"/>
-      <x:c r="F23" s="38" t="s"/>
-      <x:c r="G23" s="38" t="s"/>
-      <x:c r="H23" s="38" t="s"/>
-      <x:c r="I23" s="38" t="s"/>
-      <x:c r="J23" s="38" t="s"/>
-      <x:c r="K23" s="38" t="s"/>
-      <x:c r="L23" s="38" t="s"/>
-      <x:c r="M23" s="38" t="s"/>
-      <x:c r="N23" s="38" t="s"/>
-      <x:c r="O23" s="38" t="s"/>
-      <x:c r="P23" s="38" t="s"/>
-      <x:c r="Q23" s="38" t="s"/>
-      <x:c r="R23" s="38" t="s"/>
-      <x:c r="S23" s="38" t="s"/>
-      <x:c r="T23" s="38" t="s"/>
-      <x:c r="U23" s="38" t="s"/>
-      <x:c r="V23" s="38" t="s"/>
-      <x:c r="W23" s="38" t="s"/>
-      <x:c r="X23" s="38" t="s"/>
-      <x:c r="Y23" s="38" t="s"/>
-      <x:c r="Z23" s="38" t="s"/>
-      <x:c r="AA23" s="38" t="s"/>
-      <x:c r="AB23" s="38" t="s"/>
-      <x:c r="AC23" s="38" t="s"/>
-      <x:c r="AD23" s="38" t="s"/>
-      <x:c r="AE23" s="38" t="s"/>
-      <x:c r="AF23" s="38" t="s"/>
-      <x:c r="AG23" s="38" t="s"/>
-      <x:c r="AH23" s="38" t="s"/>
-      <x:c r="AI23" s="38" t="s"/>
-      <x:c r="AJ23" s="38" t="s"/>
-      <x:c r="AK23" s="38" t="s"/>
-      <x:c r="AL23" s="38" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AM23" s="38" t="s"/>
-      <x:c r="AN23" s="38" t="s"/>
-      <x:c r="AO23" s="38" t="s"/>
-      <x:c r="AP23" s="38" t="s"/>
-      <x:c r="AQ23" s="38" t="s"/>
-      <x:c r="AR23" s="38" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="AS23" s="38" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="AT23" s="38" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="AU23" s="38" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="AV23" s="38" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AW23" s="38" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="AX23" s="38" t="s"/>
-      <x:c r="AY23" s="38" t="s"/>
-      <x:c r="AZ23" s="38" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA23" s="38" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BB23" s="38" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="BC23" s="38" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="BD23" s="38" t="s"/>
-      <x:c r="BE23" s="38" t="s"/>
-      <x:c r="BF23" s="38" t="s"/>
-      <x:c r="BG23" s="38" t="s"/>
-      <x:c r="BH23" s="38" t="s"/>
-      <x:c r="BI23" s="38" t="s"/>
-      <x:c r="BJ23" s="38" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:62" ht="79.2" customHeight="1">
-      <x:c r="A24" s="23" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="B24" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="D24" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="H24" s="14" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="I24" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="J24" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="K24" s="14" t="s"/>
-      <x:c r="L24" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="N24" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="O24" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="P24" s="14" t="s"/>
-      <x:c r="Q24" s="14" t="s"/>
-      <x:c r="R24" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="S24" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="T24" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="U24" s="14" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="V24" s="14" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="W24" s="14" t="s"/>
-      <x:c r="X24" s="14" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="Y24" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="Z24" s="14" t="s"/>
-      <x:c r="AA24" s="14" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="AB24" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="AC24" s="14" t="s"/>
-      <x:c r="AD24" s="14" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="AE24" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AF24" s="14" t="s"/>
-      <x:c r="AG24" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="AH24" s="14" t="s"/>
-      <x:c r="AI24" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="AJ24" s="14" t="s"/>
-      <x:c r="AK24" s="14" t="s"/>
-      <x:c r="AL24" s="18" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="AM24" s="14" t="s"/>
-      <x:c r="AN24" s="14" t="s"/>
-      <x:c r="AO24" s="14" t="s"/>
-      <x:c r="AP24" s="14" t="s"/>
-      <x:c r="AQ24" s="14" t="s"/>
-      <x:c r="AR24" s="14" t="s"/>
-      <x:c r="AS24" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AT24" s="18" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="AU24" s="14" t="s"/>
-      <x:c r="AV24" s="14" t="s"/>
-      <x:c r="AW24" s="14" t="s"/>
-      <x:c r="AX24" s="14" t="s"/>
-      <x:c r="AY24" s="14" t="s"/>
-      <x:c r="AZ24" s="14" t="s"/>
-      <x:c r="BA24" s="14" t="s"/>
-      <x:c r="BB24" s="14" t="s"/>
-      <x:c r="BC24" s="14" t="s"/>
-      <x:c r="BD24" s="14" t="s"/>
-      <x:c r="BE24" s="14" t="s"/>
-      <x:c r="BF24" s="14" t="s"/>
-      <x:c r="BG24" s="14" t="s"/>
-      <x:c r="BH24" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI24" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BJ24" s="14" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:62" ht="66" customHeight="1">
-      <x:c r="A25" s="24" t="s"/>
-      <x:c r="B25" s="13" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D25" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H25" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I25" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="J25" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="K25" s="14" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="L25" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="N25" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="O25" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="P25" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="Q25" s="14" t="s"/>
-      <x:c r="R25" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="S25" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="T25" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="U25" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="V25" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="W25" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="X25" s="14" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="Y25" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="Z25" s="14" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="AA25" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="AB25" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="AC25" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="AD25" s="14" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="AE25" s="14" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="AF25" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="AG25" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="AH25" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="AI25" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="AJ25" s="18" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="AK25" s="14" t="s"/>
-      <x:c r="AL25" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="AM25" s="14" t="s"/>
-      <x:c r="AN25" s="14" t="s"/>
-      <x:c r="AO25" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="AP25" s="14" t="s"/>
-      <x:c r="AQ25" s="14" t="s"/>
-      <x:c r="AR25" s="14" t="s"/>
-      <x:c r="AS25" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="AT25" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AU25" s="14" t="s"/>
-      <x:c r="AV25" s="14" t="s"/>
-      <x:c r="AW25" s="14" t="s"/>
-      <x:c r="AX25" s="14" t="s"/>
-      <x:c r="AY25" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AZ25" s="14" t="s"/>
-      <x:c r="BA25" s="14" t="s"/>
-      <x:c r="BB25" s="14" t="s"/>
-      <x:c r="BC25" s="14" t="s"/>
-      <x:c r="BD25" s="14" t="s"/>
-      <x:c r="BE25" s="14" t="s"/>
-      <x:c r="BF25" s="14" t="s"/>
-      <x:c r="BG25" s="14" t="s">
+      <x:c r="BB41" s="44" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="BC41" s="44" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="BD41" s="44" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="BE41" s="44" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="BF41" s="44" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="BH25" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI25" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BJ25" s="14" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A26" s="24" t="s"/>
-      <x:c r="B26" s="13" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D26" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H26" s="14" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="I26" s="14" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="J26" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="K26" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="L26" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="N26" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="O26" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="P26" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="Q26" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="R26" s="14" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="S26" s="14" t="s"/>
-      <x:c r="T26" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="U26" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="V26" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="W26" s="14" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="X26" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Y26" s="14" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="Z26" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="AA26" s="14" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="AB26" s="14" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="AC26" s="14" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="AD26" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="AE26" s="14" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="AF26" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="AG26" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="AH26" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="AI26" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="AJ26" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="AK26" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="AL26" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="AM26" s="14" t="s"/>
-      <x:c r="AN26" s="14" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="AO26" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="AP26" s="14" t="s"/>
-      <x:c r="AQ26" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="AR26" s="14" t="s"/>
-      <x:c r="AS26" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="AT26" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="AU26" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AV26" s="14" t="s"/>
-      <x:c r="AW26" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="AX26" s="14" t="s"/>
-      <x:c r="AY26" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="AZ26" s="14" t="s"/>
-      <x:c r="BA26" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="BB26" s="18" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="BC26" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="BD26" s="14" t="s"/>
-      <x:c r="BE26" s="14" t="s"/>
-      <x:c r="BF26" s="14" t="s"/>
-      <x:c r="BG26" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BH26" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI26" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BJ26" s="14" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A27" s="24" t="s"/>
-      <x:c r="B27" s="13" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s"/>
-      <x:c r="D27" s="14" t="s"/>
-      <x:c r="E27" s="14" t="s"/>
-      <x:c r="F27" s="14" t="s"/>
-      <x:c r="G27" s="14" t="s"/>
-      <x:c r="H27" s="14" t="s"/>
-      <x:c r="I27" s="14" t="s"/>
-      <x:c r="J27" s="14" t="s"/>
-      <x:c r="K27" s="14" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="L27" s="14" t="s"/>
-      <x:c r="M27" s="14" t="s"/>
-      <x:c r="N27" s="14" t="s"/>
-      <x:c r="O27" s="14" t="s"/>
-      <x:c r="P27" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="Q27" s="14" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="R27" s="14" t="s"/>
-      <x:c r="S27" s="14" t="s"/>
-      <x:c r="T27" s="14" t="s"/>
-      <x:c r="U27" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="V27" s="14" t="s"/>
-      <x:c r="W27" s="14" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="X27" s="14" t="s"/>
-      <x:c r="Y27" s="14" t="s"/>
-      <x:c r="Z27" s="14" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="AA27" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AB27" s="18" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="AC27" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="AD27" s="14" t="s"/>
-      <x:c r="AE27" s="14" t="s"/>
-      <x:c r="AF27" s="14" t="s"/>
-      <x:c r="AG27" s="14" t="s"/>
-      <x:c r="AH27" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="AI27" s="14" t="s"/>
-      <x:c r="AJ27" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="AK27" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="AL27" s="14" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="AM27" s="14" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="AN27" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="AO27" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="AP27" s="14" t="s"/>
-      <x:c r="AQ27" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="AR27" s="14" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="AS27" s="14" t="s"/>
-      <x:c r="AT27" s="14" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="AU27" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AV27" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="AW27" s="14" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="AX27" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="AY27" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="AZ27" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA27" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="BB27" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="BC27" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="BD27" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="BE27" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="BF27" s="14" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="BG27" s="14" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="BH27" s="14" t="s"/>
-      <x:c r="BI27" s="14" t="s"/>
-      <x:c r="BJ27" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A28" s="24" t="s"/>
-      <x:c r="B28" s="13" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s"/>
-      <x:c r="D28" s="14" t="s"/>
-      <x:c r="E28" s="14" t="s"/>
-      <x:c r="F28" s="14" t="s"/>
-      <x:c r="G28" s="14" t="s"/>
-      <x:c r="H28" s="14" t="s"/>
-      <x:c r="I28" s="14" t="s"/>
-      <x:c r="J28" s="14" t="s"/>
-      <x:c r="K28" s="14" t="s"/>
-      <x:c r="L28" s="14" t="s"/>
-      <x:c r="M28" s="14" t="s"/>
-      <x:c r="N28" s="14" t="s"/>
-      <x:c r="O28" s="14" t="s"/>
-      <x:c r="P28" s="14" t="s"/>
-      <x:c r="Q28" s="14" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="R28" s="14" t="s"/>
-      <x:c r="S28" s="14" t="s"/>
-      <x:c r="T28" s="14" t="s"/>
-      <x:c r="U28" s="14" t="s"/>
-      <x:c r="V28" s="14" t="s"/>
-      <x:c r="W28" s="14" t="s"/>
-      <x:c r="X28" s="14" t="s"/>
-      <x:c r="Y28" s="14" t="s"/>
-      <x:c r="Z28" s="14" t="s"/>
-      <x:c r="AA28" s="14" t="s"/>
-      <x:c r="AB28" s="14" t="s"/>
-      <x:c r="AC28" s="14" t="s"/>
-      <x:c r="AD28" s="14" t="s"/>
-      <x:c r="AE28" s="14" t="s"/>
-      <x:c r="AF28" s="14" t="s"/>
-      <x:c r="AG28" s="14" t="s"/>
-      <x:c r="AH28" s="14" t="s"/>
-      <x:c r="AI28" s="14" t="s"/>
-      <x:c r="AJ28" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AK28" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="AL28" s="14" t="s"/>
-      <x:c r="AM28" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="AN28" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="AO28" s="14" t="s"/>
-      <x:c r="AP28" s="14" t="s"/>
-      <x:c r="AQ28" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="AR28" s="14" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="AS28" s="14" t="s"/>
-      <x:c r="AT28" s="14" t="s"/>
-      <x:c r="AU28" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="AV28" s="14" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="AW28" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="AX28" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="AY28" s="14" t="s"/>
-      <x:c r="AZ28" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA28" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="BB28" s="14" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="BC28" s="14" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="BD28" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="BE28" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="BF28" s="14" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="BG28" s="14" t="s"/>
-      <x:c r="BH28" s="14" t="s"/>
-      <x:c r="BI28" s="14" t="s"/>
-      <x:c r="BJ28" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A29" s="25" t="s"/>
-      <x:c r="B29" s="13" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s"/>
-      <x:c r="D29" s="14" t="s"/>
-      <x:c r="E29" s="14" t="s"/>
-      <x:c r="F29" s="14" t="s"/>
-      <x:c r="G29" s="14" t="s"/>
-      <x:c r="H29" s="14" t="s"/>
-      <x:c r="I29" s="14" t="s"/>
-      <x:c r="J29" s="14" t="s"/>
-      <x:c r="K29" s="14" t="s"/>
-      <x:c r="L29" s="14" t="s"/>
-      <x:c r="M29" s="14" t="s"/>
-      <x:c r="N29" s="14" t="s"/>
-      <x:c r="O29" s="14" t="s"/>
-      <x:c r="P29" s="14" t="s"/>
-      <x:c r="Q29" s="14" t="s"/>
-      <x:c r="R29" s="14" t="s"/>
-      <x:c r="S29" s="14" t="s"/>
-      <x:c r="T29" s="14" t="s"/>
-      <x:c r="U29" s="14" t="s"/>
-      <x:c r="V29" s="14" t="s"/>
-      <x:c r="W29" s="14" t="s"/>
-      <x:c r="X29" s="14" t="s"/>
-      <x:c r="Y29" s="14" t="s"/>
-      <x:c r="Z29" s="14" t="s"/>
-      <x:c r="AA29" s="14" t="s"/>
-      <x:c r="AB29" s="14" t="s"/>
-      <x:c r="AC29" s="14" t="s"/>
-      <x:c r="AD29" s="14" t="s"/>
-      <x:c r="AE29" s="14" t="s"/>
-      <x:c r="AF29" s="14" t="s"/>
-      <x:c r="AG29" s="14" t="s"/>
-      <x:c r="AH29" s="14" t="s"/>
-      <x:c r="AI29" s="14" t="s"/>
-      <x:c r="AJ29" s="14" t="s"/>
-      <x:c r="AK29" s="14" t="s"/>
-      <x:c r="AL29" s="14" t="s"/>
-      <x:c r="AM29" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="AN29" s="14" t="s"/>
-      <x:c r="AO29" s="14" t="s"/>
-      <x:c r="AP29" s="14" t="s"/>
-      <x:c r="AQ29" s="14" t="s"/>
-      <x:c r="AR29" s="14" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="AS29" s="14" t="s"/>
-      <x:c r="AT29" s="14" t="s"/>
-      <x:c r="AU29" s="14" t="s"/>
-      <x:c r="AV29" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="AW29" s="14" t="s"/>
-      <x:c r="AX29" s="14" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="AY29" s="14" t="s"/>
-      <x:c r="AZ29" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA29" s="14" t="s"/>
-      <x:c r="BB29" s="14" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="BC29" s="14" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="BD29" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="BE29" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="BF29" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BG29" s="14" t="s"/>
-      <x:c r="BH29" s="14" t="s"/>
-      <x:c r="BI29" s="14" t="s"/>
-      <x:c r="BJ29" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A30" s="35" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="B30" s="36" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C30" s="38" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D30" s="38" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="E30" s="38" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F30" s="38" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G30" s="38" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H30" s="38" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="I30" s="38" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="J30" s="39" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K30" s="38" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="L30" s="39" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="M30" s="38" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="N30" s="38" t="s"/>
-      <x:c r="O30" s="38" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="P30" s="38" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="Q30" s="38" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="R30" s="38" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="S30" s="38" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="T30" s="38" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="U30" s="38" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="V30" s="38" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="W30" s="38" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="X30" s="38" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="Y30" s="38" t="s"/>
-      <x:c r="Z30" s="38" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="AA30" s="38" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="AB30" s="38" t="s"/>
-      <x:c r="AC30" s="38" t="s"/>
-      <x:c r="AD30" s="39" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="AE30" s="38" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="AF30" s="38" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AG30" s="38" t="s"/>
-      <x:c r="AH30" s="38" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="AI30" s="38" t="s"/>
-      <x:c r="AJ30" s="38" t="s"/>
-      <x:c r="AK30" s="38" t="s"/>
-      <x:c r="AL30" s="38" t="s"/>
-      <x:c r="AM30" s="38" t="s"/>
-      <x:c r="AN30" s="38" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="AO30" s="38" t="s"/>
-      <x:c r="AP30" s="38" t="s"/>
-      <x:c r="AQ30" s="38" t="s"/>
-      <x:c r="AR30" s="38" t="s"/>
-      <x:c r="AS30" s="38" t="s"/>
-      <x:c r="AT30" s="38" t="s"/>
-      <x:c r="AU30" s="38" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="AV30" s="39" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="AW30" s="38" t="s"/>
-      <x:c r="AX30" s="38" t="s"/>
-      <x:c r="AY30" s="38" t="s"/>
-      <x:c r="AZ30" s="38" t="s"/>
-      <x:c r="BA30" s="38" t="s"/>
-      <x:c r="BB30" s="38" t="s"/>
-      <x:c r="BC30" s="38" t="s"/>
-      <x:c r="BD30" s="38" t="s"/>
-      <x:c r="BE30" s="38" t="s"/>
-      <x:c r="BF30" s="38" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BG30" s="38" t="s"/>
-      <x:c r="BH30" s="38" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI30" s="38" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BJ30" s="38" t="s"/>
-    </x:row>
-    <x:row r="31" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A31" s="40" t="s"/>
-      <x:c r="B31" s="36" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C31" s="38" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D31" s="38" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E31" s="38" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F31" s="38" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="G31" s="38" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="H31" s="38" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="I31" s="38" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="J31" s="38" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="K31" s="38" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="L31" s="38" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="M31" s="38" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="N31" s="38" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="O31" s="38" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="P31" s="39" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="Q31" s="38" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="R31" s="38" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="S31" s="38" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="T31" s="38" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="U31" s="38" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="V31" s="38" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="W31" s="38" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="X31" s="38" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="Y31" s="38" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="Z31" s="38" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="AA31" s="38" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="AB31" s="38" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="AC31" s="38" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AD31" s="38" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="AE31" s="38" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="AF31" s="38" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AG31" s="38" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="AH31" s="38" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="AI31" s="38" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="AJ31" s="38" t="s"/>
-      <x:c r="AK31" s="38" t="s"/>
-      <x:c r="AL31" s="38" t="s"/>
-      <x:c r="AM31" s="38" t="s"/>
-      <x:c r="AN31" s="38" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="AO31" s="38" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="AP31" s="38" t="s"/>
-      <x:c r="AQ31" s="38" t="s"/>
-      <x:c r="AR31" s="38" t="s"/>
-      <x:c r="AS31" s="38" t="s"/>
-      <x:c r="AT31" s="38" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AU31" s="38" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="AV31" s="38" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="AW31" s="39" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="AX31" s="38" t="s"/>
-      <x:c r="AY31" s="38" t="s"/>
-      <x:c r="AZ31" s="38" t="s"/>
-      <x:c r="BA31" s="38" t="s"/>
-      <x:c r="BB31" s="38" t="s"/>
-      <x:c r="BC31" s="38" t="s"/>
-      <x:c r="BD31" s="38" t="s"/>
-      <x:c r="BE31" s="38" t="s"/>
-      <x:c r="BF31" s="38" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BG31" s="38" t="s"/>
-      <x:c r="BH31" s="38" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI31" s="38" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BJ31" s="38" t="s"/>
-    </x:row>
-    <x:row r="32" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A32" s="40" t="s"/>
-      <x:c r="B32" s="36" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C32" s="38" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D32" s="38" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="E32" s="38" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="F32" s="38" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G32" s="38" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H32" s="38" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="I32" s="39" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="J32" s="38" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="K32" s="38" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="L32" s="38" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="M32" s="38" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="N32" s="38" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="O32" s="38" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="P32" s="38" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="Q32" s="38" t="s"/>
-      <x:c r="R32" s="38" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="S32" s="38" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="T32" s="38" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="U32" s="38" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="V32" s="38" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="W32" s="38" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="X32" s="38" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="Y32" s="38" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="Z32" s="38" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="AA32" s="38" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="AB32" s="38" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="AC32" s="38" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="AD32" s="38" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AE32" s="38" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="AF32" s="38" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="AG32" s="38" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="AH32" s="38" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="AI32" s="38" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="AJ32" s="38" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="AK32" s="38" t="s">
-        <x:v>339</x:v>
-      </x:c>
-      <x:c r="AL32" s="38" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="AM32" s="38" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AN32" s="38" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="AO32" s="38" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="AP32" s="38" t="s"/>
-      <x:c r="AQ32" s="38" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="AR32" s="38" t="s"/>
-      <x:c r="AS32" s="39" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="AT32" s="38" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="AU32" s="38" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="AV32" s="38" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="AW32" s="38" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="AX32" s="38" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="AY32" s="38" t="s"/>
-      <x:c r="AZ32" s="39" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="BA32" s="38" t="s"/>
-      <x:c r="BB32" s="38" t="s"/>
-      <x:c r="BC32" s="38" t="s"/>
-      <x:c r="BD32" s="38" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="BE32" s="38" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="BF32" s="38" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="BG32" s="38" t="s"/>
-      <x:c r="BH32" s="38" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI32" s="38" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BJ32" s="38" t="s"/>
-    </x:row>
-    <x:row r="33" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A33" s="40" t="s"/>
-      <x:c r="B33" s="36" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C33" s="38" t="s"/>
-      <x:c r="D33" s="38" t="s"/>
-      <x:c r="E33" s="38" t="s"/>
-      <x:c r="F33" s="38" t="s"/>
-      <x:c r="G33" s="38" t="s"/>
-      <x:c r="H33" s="38" t="s"/>
-      <x:c r="I33" s="38" t="s"/>
-      <x:c r="J33" s="38" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K33" s="38" t="s"/>
-      <x:c r="L33" s="38" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="M33" s="39" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N33" s="38" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="O33" s="38" t="s"/>
-      <x:c r="P33" s="38" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="Q33" s="38" t="s"/>
-      <x:c r="R33" s="38" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="S33" s="38" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="T33" s="38" t="s"/>
-      <x:c r="U33" s="38" t="s"/>
-      <x:c r="V33" s="38" t="s"/>
-      <x:c r="W33" s="38" t="s"/>
-      <x:c r="X33" s="38" t="s"/>
-      <x:c r="Y33" s="38" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="Z33" s="38" t="s"/>
-      <x:c r="AA33" s="38" t="s"/>
-      <x:c r="AB33" s="38" t="s"/>
-      <x:c r="AC33" s="38" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AD33" s="38" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="AE33" s="38" t="s"/>
-      <x:c r="AF33" s="38" t="s"/>
-      <x:c r="AG33" s="38" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AH33" s="38" t="s"/>
-      <x:c r="AI33" s="38" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="AJ33" s="38" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="AK33" s="38" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="AL33" s="38" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="AM33" s="38" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="AN33" s="38" t="s"/>
-      <x:c r="AO33" s="38" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="AP33" s="38" t="s"/>
-      <x:c r="AQ33" s="38" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="AR33" s="38" t="s">
-        <x:v>346</x:v>
-      </x:c>
-      <x:c r="AS33" s="38" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="AT33" s="38" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="AU33" s="38" t="s"/>
-      <x:c r="AV33" s="38" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="AW33" s="38" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="AX33" s="38" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="AY33" s="38" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="AZ33" s="38" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA33" s="38" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="BB33" s="38" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="BC33" s="38" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="BD33" s="38" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="BE33" s="38" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="BF33" s="38" t="s"/>
-      <x:c r="BG33" s="38" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BH33" s="38" t="s"/>
-      <x:c r="BI33" s="38" t="s"/>
-      <x:c r="BJ33" s="38" t="s">
-        <x:v>214</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A34" s="40" t="s"/>
-      <x:c r="B34" s="36" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="C34" s="38" t="s"/>
-      <x:c r="D34" s="38" t="s"/>
-      <x:c r="E34" s="38" t="s"/>
-      <x:c r="F34" s="38" t="s"/>
-      <x:c r="G34" s="38" t="s"/>
-      <x:c r="H34" s="38" t="s"/>
-      <x:c r="I34" s="38" t="s"/>
-      <x:c r="J34" s="38" t="s"/>
-      <x:c r="K34" s="38" t="s"/>
-      <x:c r="L34" s="38" t="s"/>
-      <x:c r="M34" s="38" t="s"/>
-      <x:c r="N34" s="38" t="s"/>
-      <x:c r="O34" s="38" t="s"/>
-      <x:c r="P34" s="38" t="s"/>
-      <x:c r="Q34" s="38" t="s"/>
-      <x:c r="R34" s="38" t="s"/>
-      <x:c r="S34" s="38" t="s"/>
-      <x:c r="T34" s="38" t="s"/>
-      <x:c r="U34" s="38" t="s"/>
-      <x:c r="V34" s="38" t="s"/>
-      <x:c r="W34" s="38" t="s"/>
-      <x:c r="X34" s="38" t="s"/>
-      <x:c r="Y34" s="38" t="s"/>
-      <x:c r="Z34" s="38" t="s"/>
-      <x:c r="AA34" s="38" t="s"/>
-      <x:c r="AB34" s="38" t="s"/>
-      <x:c r="AC34" s="38" t="s"/>
-      <x:c r="AD34" s="38" t="s"/>
-      <x:c r="AE34" s="38" t="s"/>
-      <x:c r="AF34" s="38" t="s"/>
-      <x:c r="AG34" s="38" t="s"/>
-      <x:c r="AH34" s="38" t="s"/>
-      <x:c r="AI34" s="38" t="s"/>
-      <x:c r="AJ34" s="38" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="AK34" s="38" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="AL34" s="38" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AM34" s="38" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AN34" s="38" t="s"/>
-      <x:c r="AO34" s="38" t="s"/>
-      <x:c r="AP34" s="38" t="s"/>
-      <x:c r="AQ34" s="38" t="s">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c r="AR34" s="38" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="AS34" s="38" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="AT34" s="38" t="s"/>
-      <x:c r="AU34" s="38" t="s"/>
-      <x:c r="AV34" s="38" t="s"/>
-      <x:c r="AW34" s="38" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="AX34" s="38" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="AY34" s="38" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="AZ34" s="38" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA34" s="38" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="BB34" s="38" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="BC34" s="38" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="BD34" s="38" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="BE34" s="38" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="BF34" s="38" t="s"/>
-      <x:c r="BG34" s="38" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BH34" s="38" t="s"/>
-      <x:c r="BI34" s="38" t="s"/>
-      <x:c r="BJ34" s="38" t="s">
-        <x:v>214</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A35" s="42" t="s"/>
-      <x:c r="B35" s="36" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="C35" s="38" t="s"/>
-      <x:c r="D35" s="38" t="s"/>
-      <x:c r="E35" s="38" t="s"/>
-      <x:c r="F35" s="38" t="s"/>
-      <x:c r="G35" s="38" t="s"/>
-      <x:c r="H35" s="38" t="s"/>
-      <x:c r="I35" s="38" t="s"/>
-      <x:c r="J35" s="38" t="s"/>
-      <x:c r="K35" s="38" t="s"/>
-      <x:c r="L35" s="38" t="s"/>
-      <x:c r="M35" s="38" t="s"/>
-      <x:c r="N35" s="38" t="s"/>
-      <x:c r="O35" s="38" t="s"/>
-      <x:c r="P35" s="38" t="s"/>
-      <x:c r="Q35" s="38" t="s"/>
-      <x:c r="R35" s="38" t="s"/>
-      <x:c r="S35" s="38" t="s"/>
-      <x:c r="T35" s="38" t="s"/>
-      <x:c r="U35" s="38" t="s"/>
-      <x:c r="V35" s="38" t="s"/>
-      <x:c r="W35" s="38" t="s"/>
-      <x:c r="X35" s="38" t="s"/>
-      <x:c r="Y35" s="38" t="s"/>
-      <x:c r="Z35" s="38" t="s"/>
-      <x:c r="AA35" s="38" t="s"/>
-      <x:c r="AB35" s="38" t="s"/>
-      <x:c r="AC35" s="38" t="s"/>
-      <x:c r="AD35" s="38" t="s"/>
-      <x:c r="AE35" s="38" t="s"/>
-      <x:c r="AF35" s="38" t="s"/>
-      <x:c r="AG35" s="38" t="s"/>
-      <x:c r="AH35" s="38" t="s"/>
-      <x:c r="AI35" s="38" t="s"/>
-      <x:c r="AJ35" s="38" t="s"/>
-      <x:c r="AK35" s="38" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AL35" s="38" t="s"/>
-      <x:c r="AM35" s="38" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="AN35" s="38" t="s"/>
-      <x:c r="AO35" s="38" t="s"/>
-      <x:c r="AP35" s="38" t="s"/>
-      <x:c r="AQ35" s="39" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="AR35" s="38" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="AS35" s="38" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="AT35" s="38" t="s"/>
-      <x:c r="AU35" s="38" t="s"/>
-      <x:c r="AV35" s="38" t="s"/>
-      <x:c r="AW35" s="38" t="s"/>
-      <x:c r="AX35" s="38" t="s"/>
-      <x:c r="AY35" s="38" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="AZ35" s="38" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA35" s="38" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BB35" s="38" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="BC35" s="38" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="BD35" s="38" t="s"/>
-      <x:c r="BE35" s="38" t="s"/>
-      <x:c r="BF35" s="38" t="s"/>
-      <x:c r="BG35" s="38" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BH35" s="38" t="s"/>
-      <x:c r="BI35" s="38" t="s"/>
-      <x:c r="BJ35" s="38" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:62" ht="79.2" customHeight="1">
-      <x:c r="A36" s="23" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="B36" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D36" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="H36" s="14" t="s"/>
-      <x:c r="I36" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="J36" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="K36" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="L36" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="N36" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="O36" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="P36" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="Q36" s="14" t="s"/>
-      <x:c r="R36" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="S36" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="T36" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="U36" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="V36" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="W36" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="X36" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="Y36" s="14" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="Z36" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="AA36" s="14" t="s"/>
-      <x:c r="AB36" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="AC36" s="14" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="AD36" s="14" t="s"/>
-      <x:c r="AE36" s="14" t="s"/>
-      <x:c r="AF36" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="AG36" s="14" t="s"/>
-      <x:c r="AH36" s="14" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="AI36" s="14" t="s"/>
-      <x:c r="AJ36" s="14" t="s"/>
-      <x:c r="AK36" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="AL36" s="14" t="s"/>
-      <x:c r="AM36" s="14" t="s"/>
-      <x:c r="AN36" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="AO36" s="14" t="s"/>
-      <x:c r="AP36" s="14" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="AQ36" s="14" t="s"/>
-      <x:c r="AR36" s="14" t="s"/>
-      <x:c r="AS36" s="14" t="s"/>
-      <x:c r="AT36" s="14" t="s"/>
-      <x:c r="AU36" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="AV36" s="14" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="AW36" s="14" t="s"/>
-      <x:c r="AX36" s="14" t="s"/>
-      <x:c r="AY36" s="14" t="s"/>
-      <x:c r="AZ36" s="14" t="s"/>
-      <x:c r="BA36" s="14" t="s"/>
-      <x:c r="BB36" s="14" t="s"/>
-      <x:c r="BC36" s="14" t="s"/>
-      <x:c r="BD36" s="14" t="s"/>
-      <x:c r="BE36" s="14" t="s"/>
-      <x:c r="BF36" s="14" t="s"/>
-      <x:c r="BG36" s="14" t="s"/>
-      <x:c r="BH36" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI36" s="14" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="BJ36" s="14" t="s"/>
-    </x:row>
-    <x:row r="37" spans="1:62" ht="66" customHeight="1">
-      <x:c r="A37" s="24" t="s"/>
-      <x:c r="B37" s="13" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="D37" s="14" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H37" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I37" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="J37" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K37" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L37" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="N37" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="O37" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="P37" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="Q37" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="R37" s="14" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="S37" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="T37" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="U37" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="V37" s="14" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="W37" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="X37" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="Y37" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="Z37" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="AA37" s="14" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="AB37" s="14" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="AC37" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="AD37" s="14" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="AE37" s="14" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="AF37" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="AG37" s="14" t="s"/>
-      <x:c r="AH37" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="AI37" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="AJ37" s="14" t="s"/>
-      <x:c r="AK37" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="AL37" s="14" t="s"/>
-      <x:c r="AM37" s="14" t="s"/>
-      <x:c r="AN37" s="14" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="AO37" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="AP37" s="14" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="AQ37" s="14" t="s"/>
-      <x:c r="AR37" s="14" t="s"/>
-      <x:c r="AS37" s="14" t="s"/>
-      <x:c r="AT37" s="14" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="AU37" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="AV37" s="14" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="AW37" s="14" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="AX37" s="14" t="s"/>
-      <x:c r="AY37" s="14" t="s"/>
-      <x:c r="AZ37" s="14" t="s"/>
-      <x:c r="BA37" s="14" t="s"/>
-      <x:c r="BB37" s="14" t="s"/>
-      <x:c r="BC37" s="14" t="s"/>
-      <x:c r="BD37" s="14" t="s"/>
-      <x:c r="BE37" s="14" t="s"/>
-      <x:c r="BF37" s="14" t="s"/>
-      <x:c r="BG37" s="14" t="s"/>
-      <x:c r="BH37" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI37" s="14" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="BJ37" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:62" ht="79.2" customHeight="1">
-      <x:c r="A38" s="24" t="s"/>
-      <x:c r="B38" s="13" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="D38" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H38" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="I38" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="J38" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="K38" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="L38" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="N38" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="O38" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="P38" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="Q38" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="R38" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="S38" s="14" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="T38" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="U38" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="V38" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="W38" s="14" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="X38" s="14" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="Y38" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="Z38" s="14" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="AA38" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="AB38" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AC38" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="AD38" s="14" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="AE38" s="14" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="AF38" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="AG38" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="AH38" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="AI38" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="AJ38" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="AK38" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AL38" s="14" t="s"/>
-      <x:c r="AM38" s="14" t="s"/>
-      <x:c r="AN38" s="14" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="AO38" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="AP38" s="14" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="AQ38" s="14" t="s"/>
-      <x:c r="AR38" s="14" t="s"/>
-      <x:c r="AS38" s="14" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="AT38" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="AU38" s="14" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="AV38" s="14" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="AW38" s="14" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="AX38" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="AY38" s="14" t="s"/>
-      <x:c r="AZ38" s="14" t="s"/>
-      <x:c r="BA38" s="14" t="s"/>
-      <x:c r="BB38" s="14" t="s"/>
-      <x:c r="BC38" s="14" t="s"/>
-      <x:c r="BD38" s="14" t="s"/>
-      <x:c r="BE38" s="14" t="s"/>
-      <x:c r="BF38" s="14" t="s"/>
-      <x:c r="BG38" s="14" t="s"/>
-      <x:c r="BH38" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="BI38" s="14" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="BJ38" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A39" s="24" t="s"/>
-      <x:c r="B39" s="13" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s"/>
-      <x:c r="D39" s="14" t="s"/>
-      <x:c r="E39" s="14" t="s"/>
-      <x:c r="F39" s="14" t="s"/>
-      <x:c r="G39" s="14" t="s"/>
-      <x:c r="H39" s="14" t="s"/>
-      <x:c r="I39" s="14" t="s"/>
-      <x:c r="J39" s="14" t="s"/>
-      <x:c r="K39" s="14" t="s"/>
-      <x:c r="L39" s="14" t="s"/>
-      <x:c r="M39" s="14" t="s"/>
-      <x:c r="N39" s="14" t="s"/>
-      <x:c r="O39" s="14" t="s"/>
-      <x:c r="P39" s="14" t="s"/>
-      <x:c r="Q39" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="R39" s="14" t="s"/>
-      <x:c r="S39" s="14" t="s"/>
-      <x:c r="T39" s="14" t="s"/>
-      <x:c r="U39" s="14" t="s"/>
-      <x:c r="V39" s="14" t="s"/>
-      <x:c r="W39" s="14" t="s"/>
-      <x:c r="X39" s="14" t="s"/>
-      <x:c r="Y39" s="14" t="s"/>
-      <x:c r="Z39" s="14" t="s"/>
-      <x:c r="AA39" s="14" t="s"/>
-      <x:c r="AB39" s="14" t="s"/>
-      <x:c r="AC39" s="14" t="s"/>
-      <x:c r="AD39" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AE39" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="AF39" s="14" t="s"/>
-      <x:c r="AG39" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AH39" s="14" t="s"/>
-      <x:c r="AI39" s="14" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="AJ39" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AK39" s="14" t="s"/>
-      <x:c r="AL39" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="AM39" s="14" t="s"/>
-      <x:c r="AN39" s="14" t="s"/>
-      <x:c r="AO39" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="AP39" s="14" t="s"/>
-      <x:c r="AQ39" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="AR39" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="AS39" s="14" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="AT39" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="AU39" s="14" t="s"/>
-      <x:c r="AV39" s="14" t="s"/>
-      <x:c r="AW39" s="14" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="AX39" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="AY39" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="AZ39" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA39" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="BB39" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="BC39" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="BD39" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="BE39" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="BF39" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BG39" s="14" t="s">
+      <x:c r="BG41" s="44" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="BH39" s="14" t="s"/>
-      <x:c r="BI39" s="14" t="s"/>
-      <x:c r="BJ39" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A40" s="24" t="s"/>
-      <x:c r="B40" s="13" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="C40" s="14" t="s"/>
-      <x:c r="D40" s="14" t="s"/>
-      <x:c r="E40" s="14" t="s"/>
-      <x:c r="F40" s="14" t="s"/>
-      <x:c r="G40" s="14" t="s"/>
-      <x:c r="H40" s="14" t="s"/>
-      <x:c r="I40" s="14" t="s"/>
-      <x:c r="J40" s="14" t="s"/>
-      <x:c r="K40" s="14" t="s"/>
-      <x:c r="L40" s="14" t="s"/>
-      <x:c r="M40" s="14" t="s"/>
-      <x:c r="N40" s="14" t="s"/>
-      <x:c r="O40" s="14" t="s"/>
-      <x:c r="P40" s="14" t="s"/>
-      <x:c r="Q40" s="14" t="s"/>
-      <x:c r="R40" s="14" t="s"/>
-      <x:c r="S40" s="14" t="s"/>
-      <x:c r="T40" s="14" t="s"/>
-      <x:c r="U40" s="14" t="s"/>
-      <x:c r="V40" s="14" t="s"/>
-      <x:c r="W40" s="14" t="s"/>
-      <x:c r="X40" s="14" t="s"/>
-      <x:c r="Y40" s="14" t="s"/>
-      <x:c r="Z40" s="14" t="s"/>
-      <x:c r="AA40" s="14" t="s"/>
-      <x:c r="AB40" s="14" t="s"/>
-      <x:c r="AC40" s="14" t="s"/>
-      <x:c r="AD40" s="14" t="s"/>
-      <x:c r="AE40" s="14" t="s"/>
-      <x:c r="AF40" s="14" t="s"/>
-      <x:c r="AG40" s="14" t="s"/>
-      <x:c r="AH40" s="14" t="s"/>
-      <x:c r="AI40" s="14" t="s"/>
-      <x:c r="AJ40" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="AK40" s="14" t="s"/>
-      <x:c r="AL40" s="14" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="AM40" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="AN40" s="14" t="s"/>
-      <x:c r="AO40" s="14" t="s"/>
-      <x:c r="AP40" s="14" t="s"/>
-      <x:c r="AQ40" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="AR40" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="AS40" s="14" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="AT40" s="14" t="s"/>
-      <x:c r="AU40" s="14" t="s"/>
-      <x:c r="AV40" s="14" t="s"/>
-      <x:c r="AW40" s="14" t="s"/>
-      <x:c r="AX40" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AY40" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="AZ40" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA40" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="BB40" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="BC40" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="BD40" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="BE40" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="BF40" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BG40" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="BH40" s="14" t="s"/>
-      <x:c r="BI40" s="14" t="s"/>
-      <x:c r="BJ40" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:62" ht="53.4" customHeight="1">
-      <x:c r="A41" s="25" t="s"/>
-      <x:c r="B41" s="13" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="C41" s="14" t="s"/>
-      <x:c r="D41" s="14" t="s"/>
-      <x:c r="E41" s="14" t="s"/>
-      <x:c r="F41" s="14" t="s"/>
-      <x:c r="G41" s="14" t="s"/>
-      <x:c r="H41" s="14" t="s"/>
-      <x:c r="I41" s="14" t="s"/>
-      <x:c r="J41" s="14" t="s"/>
-      <x:c r="K41" s="14" t="s"/>
-      <x:c r="L41" s="14" t="s"/>
-      <x:c r="M41" s="14" t="s"/>
-      <x:c r="N41" s="14" t="s"/>
-      <x:c r="O41" s="14" t="s"/>
-      <x:c r="P41" s="14" t="s"/>
-      <x:c r="Q41" s="14" t="s"/>
-      <x:c r="R41" s="14" t="s"/>
-      <x:c r="S41" s="14" t="s"/>
-      <x:c r="T41" s="14" t="s"/>
-      <x:c r="U41" s="14" t="s"/>
-      <x:c r="V41" s="14" t="s"/>
-      <x:c r="W41" s="14" t="s"/>
-      <x:c r="X41" s="14" t="s"/>
-      <x:c r="Y41" s="14" t="s"/>
-      <x:c r="Z41" s="14" t="s"/>
-      <x:c r="AA41" s="14" t="s"/>
-      <x:c r="AB41" s="14" t="s"/>
-      <x:c r="AC41" s="14" t="s"/>
-      <x:c r="AD41" s="14" t="s"/>
-      <x:c r="AE41" s="14" t="s"/>
-      <x:c r="AF41" s="14" t="s"/>
-      <x:c r="AG41" s="14" t="s"/>
-      <x:c r="AH41" s="14" t="s"/>
-      <x:c r="AI41" s="14" t="s"/>
-      <x:c r="AJ41" s="14" t="s"/>
-      <x:c r="AK41" s="14" t="s"/>
-      <x:c r="AL41" s="14" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="AM41" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="AN41" s="14" t="s"/>
-      <x:c r="AO41" s="14" t="s"/>
-      <x:c r="AP41" s="14" t="s"/>
-      <x:c r="AQ41" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="AR41" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="AS41" s="14" t="s"/>
-      <x:c r="AT41" s="14" t="s"/>
-      <x:c r="AU41" s="14" t="s"/>
-      <x:c r="AV41" s="14" t="s"/>
-      <x:c r="AW41" s="14" t="s"/>
-      <x:c r="AX41" s="14" t="s"/>
-      <x:c r="AY41" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AZ41" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="BA41" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="BB41" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="BC41" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="BD41" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="BE41" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="BF41" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="BG41" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="BH41" s="14" t="s"/>
-      <x:c r="BI41" s="14" t="s"/>
-      <x:c r="BJ41" s="14" t="s"/>
+      <x:c r="BH41" s="44" t="s"/>
+      <x:c r="BI41" s="44" t="s"/>
+      <x:c r="BJ41" s="44" t="s"/>
     </x:row>
     <x:row r="42" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A42" s="43" t="s"/>
+      <x:c r="A42" s="48" t="s"/>
     </x:row>
     <x:row r="43" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A43" s="43" t="s"/>
+      <x:c r="A43" s="48" t="s"/>
     </x:row>
     <x:row r="44" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A44" s="43" t="s"/>
+      <x:c r="A44" s="48" t="s"/>
     </x:row>
     <x:row r="45" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A45" s="43" t="s"/>
+      <x:c r="A45" s="48" t="s"/>
     </x:row>
     <x:row r="46" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A46" s="43" t="s"/>
+      <x:c r="A46" s="48" t="s"/>
     </x:row>
     <x:row r="47" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A47" s="43" t="s"/>
+      <x:c r="A47" s="48" t="s"/>
     </x:row>
     <x:row r="48" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A48" s="43" t="s"/>
+      <x:c r="A48" s="48" t="s"/>
     </x:row>
     <x:row r="49" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A49" s="43" t="s"/>
+      <x:c r="A49" s="48" t="s"/>
     </x:row>
     <x:row r="50" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A50" s="43" t="s"/>
+      <x:c r="A50" s="48" t="s"/>
     </x:row>
     <x:row r="51" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A51" s="43" t="s"/>
+      <x:c r="A51" s="48" t="s"/>
     </x:row>
     <x:row r="52" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A52" s="43" t="s"/>
+      <x:c r="A52" s="48" t="s"/>
     </x:row>
     <x:row r="53" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A53" s="43" t="s"/>
+      <x:c r="A53" s="48" t="s"/>
     </x:row>
     <x:row r="54" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A54" s="43" t="s"/>
+      <x:c r="A54" s="48" t="s"/>
     </x:row>
     <x:row r="55" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A55" s="43" t="s"/>
+      <x:c r="A55" s="48" t="s"/>
     </x:row>
     <x:row r="56" spans="1:62" ht="12" customHeight="1">
-      <x:c r="A56" s="43" t="s"/>
+      <x:c r="A56" s="48" t="s"/>
     </x:row>
     <x:row r="57" spans="1:62" ht="12" customHeight="1"/>
     <x:row r="58" spans="1:62" ht="12" customHeight="1"/>
@@ -8292,7 +8156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{2a11be50-cad5-48d6-a179-b05773e9571f}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{b20b0958-596a-4045-a1e3-97858a60b9b8}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -8300,8 +8164,8 @@
   <x:sheetFormatPr defaultRowHeight="12.75"/>
   <x:sheetData>
     <x:row r="5" spans="1:1" ht="23.25" customHeight="1">
-      <x:c r="A5" s="44" t="s">
-        <x:v>366</x:v>
+      <x:c r="A5" s="49" t="s">
+        <x:v>365</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
